--- a/output/products.xlsx
+++ b/output/products.xlsx
@@ -676,7 +676,7 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:00+00:00</t>
+          <t>2026-10-20T01:47:38+00:00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -804,7 +804,7 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:41+00:00</t>
+          <t>2026-10-20T01:48:20+00:00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -942,7 +942,7 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:36+00:00</t>
+          <t>2026-10-20T01:48:16+00:00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1080,7 +1080,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:22+00:00</t>
+          <t>2026-10-20T01:48:01+00:00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1213,7 +1213,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:35+00:00</t>
+          <t>2026-10-20T01:48:13+00:00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1350,7 +1350,7 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:41+00:00</t>
+          <t>2026-10-20T01:49:28+00:00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:02+00:00</t>
+          <t>2026-10-20T01:48:49+00:00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1631,7 +1631,7 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:38+00:00</t>
+          <t>2026-10-20T01:48:16+00:00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1772,7 +1772,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:20+00:00</t>
+          <t>2026-10-20T01:47:57+00:00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1913,7 +1913,7 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:38+00:00</t>
+          <t>2026-10-20T01:48:18+00:00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2054,7 +2054,7 @@
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:19+00:00</t>
+          <t>2026-10-20T01:47:57+00:00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2196,7 +2196,7 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:30+00:00</t>
+          <t>2026-10-20T01:48:08+00:00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2331,7 +2331,7 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:50+00:00</t>
+          <t>2026-10-20T01:48:31+00:00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2471,7 +2471,7 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:47+00:00</t>
+          <t>2026-10-20T01:48:27+00:00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2611,7 +2611,7 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:39+00:00</t>
+          <t>2026-10-20T01:48:19+00:00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2752,7 +2752,7 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:44+00:00</t>
+          <t>2026-10-20T01:48:23+00:00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2892,7 +2892,7 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:26+00:00</t>
+          <t>2026-10-20T01:48:05+00:00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -3032,7 +3032,7 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:42+00:00</t>
+          <t>2026-10-20T01:48:22+00:00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3171,7 +3171,7 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:48+00:00</t>
+          <t>2026-10-20T01:48:31+00:00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3312,7 +3312,7 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:32+00:00</t>
+          <t>2026-10-20T01:48:11+00:00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3452,7 +3452,7 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:33+00:00</t>
+          <t>2026-10-20T01:48:13+00:00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3580,7 +3580,7 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:53+00:00</t>
+          <t>2026-10-20T01:47:31+00:00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3721,7 +3721,7 @@
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:07+00:00</t>
+          <t>2026-10-20T01:48:54+00:00</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3861,7 +3861,7 @@
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:27+00:00</t>
+          <t>2026-10-20T01:49:14+00:00</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4001,7 +4001,7 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:51+00:00</t>
+          <t>2026-10-20T01:48:34+00:00</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4140,7 +4140,7 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:34+00:00</t>
+          <t>2026-10-20T01:49:22+00:00</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4281,7 +4281,7 @@
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:22+00:00</t>
+          <t>2026-10-20T01:47:58+00:00</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4420,7 +4420,7 @@
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:29+00:00</t>
+          <t>2026-10-20T01:48:09+00:00</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4560,7 +4560,7 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:18+00:00</t>
+          <t>2026-10-20T01:47:54+00:00</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4694,7 +4694,7 @@
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:09+00:00</t>
+          <t>2026-10-20T01:48:57+00:00</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4828,7 +4828,7 @@
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:25+00:00</t>
+          <t>2026-10-20T01:48:02+00:00</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4968,7 +4968,7 @@
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:49+00:00</t>
+          <t>2026-10-20T01:49:36+00:00</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -5108,7 +5108,7 @@
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:35+00:00</t>
+          <t>2026-10-20T01:48:14+00:00</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5246,7 +5246,7 @@
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:03+00:00</t>
+          <t>2026-10-20T01:48:49+00:00</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5374,7 +5374,7 @@
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:52+00:00</t>
+          <t>2026-10-20T01:47:28+00:00</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5496,7 +5496,7 @@
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:07+00:00</t>
+          <t>2026-10-20T01:47:46+00:00</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5632,7 +5632,7 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:42+00:00</t>
+          <t>2026-10-20T01:47:20+00:00</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5773,7 +5773,7 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:09+00:00</t>
+          <t>2026-10-20T01:46:50+00:00</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5936,7 +5936,7 @@
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:44+00:00</t>
+          <t>2026-10-20T01:48:26+00:00</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6075,7 +6075,7 @@
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:16+00:00</t>
+          <t>2026-10-20T01:49:04+00:00</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:25+00:00</t>
+          <t>2026-10-20T01:49:12+00:00</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6355,7 +6355,7 @@
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:11+00:00</t>
+          <t>2026-10-20T01:48:58+00:00</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6494,7 +6494,7 @@
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:17+00:00</t>
+          <t>2026-10-20T01:49:04+00:00</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6630,7 +6630,7 @@
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:08+00:00</t>
+          <t>2026-10-20T01:48:56+00:00</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6756,7 +6756,7 @@
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:31+00:00</t>
+          <t>2026-10-20T01:47:09+00:00</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6896,7 +6896,7 @@
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:30+00:00</t>
+          <t>2026-10-20T01:49:17+00:00</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -7024,7 +7024,7 @@
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:55+00:00</t>
+          <t>2026-10-20T01:47:34+00:00</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -7161,7 +7161,7 @@
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:03+00:00</t>
+          <t>2026-10-20T01:47:39+00:00</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7289,7 +7289,7 @@
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:59+00:00</t>
+          <t>2026-10-20T01:47:36+00:00</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7422,7 +7422,7 @@
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:37+00:00</t>
+          <t>2026-10-20T01:49:24+00:00</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7557,7 +7557,7 @@
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:22+00:00</t>
+          <t>2026-10-20T01:49:08+00:00</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7689,7 +7689,7 @@
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:26+00:00</t>
+          <t>2026-10-20T01:47:04+00:00</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -7831,7 +7831,7 @@
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:01+00:00</t>
+          <t>2026-10-20T01:48:46+00:00</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -7965,7 +7965,7 @@
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:15+00:00</t>
+          <t>2026-10-20T01:46:57+00:00</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -8106,7 +8106,7 @@
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:34+00:00</t>
+          <t>2026-10-20T01:49:20+00:00</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8241,7 +8241,7 @@
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:09+00:00</t>
+          <t>2026-10-20T01:46:50+00:00</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8379,12 +8379,12 @@
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:29+00:00</t>
+          <t>2026-10-20T01:48:05+00:00</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>32caba114b8338d8</t>
+          <t>24de449dfa0e84b9</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:40+00:00</t>
+          <t>2026-10-20T01:47:19+00:00</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8641,7 +8641,7 @@
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:58+00:00</t>
+          <t>2026-10-20T01:49:47+00:00</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8767,7 +8767,7 @@
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:45+00:00</t>
+          <t>2026-10-20T01:48:27+00:00</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8912,7 +8912,7 @@
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:26+00:00</t>
+          <t>2026-10-20T01:47:05+00:00</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:12+00:00</t>
+          <t>2026-10-20T01:47:49+00:00</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -9172,7 +9172,7 @@
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:21+00:00</t>
+          <t>2026-10-20T01:47:02+00:00</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9298,7 +9298,7 @@
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:52+00:00</t>
+          <t>2026-10-20T01:47:30+00:00</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
@@ -9431,7 +9431,7 @@
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:13+00:00</t>
+          <t>2026-10-20T01:46:54+00:00</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9571,7 +9571,7 @@
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:45+00:00</t>
+          <t>2026-10-20T01:49:32+00:00</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9712,7 +9712,7 @@
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:05+00:00</t>
+          <t>2026-10-20T01:48:53+00:00</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9840,7 +9840,7 @@
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:48+00:00</t>
+          <t>2026-10-20T01:47:25+00:00</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -9966,7 +9966,7 @@
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:08+00:00</t>
+          <t>2026-10-20T01:47:46+00:00</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -10088,7 +10088,7 @@
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:55+00:00</t>
+          <t>2026-10-20T01:47:32+00:00</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
@@ -10222,7 +10222,7 @@
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:59+00:00</t>
+          <t>2026-10-20T01:47:38+00:00</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -10363,7 +10363,7 @@
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:16+00:00</t>
+          <t>2026-10-20T01:47:53+00:00</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -10495,7 +10495,7 @@
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:32+00:00</t>
+          <t>2026-10-20T01:47:09+00:00</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10635,7 +10635,7 @@
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:18+00:00</t>
+          <t>2026-10-20T01:49:05+00:00</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -10770,7 +10770,7 @@
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-19T20:45:00+00:00</t>
+          <t>2026-10-20T01:49:47+00:00</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10903,7 +10903,7 @@
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:56+00:00</t>
+          <t>2026-10-20T01:49:44+00:00</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -11044,7 +11044,7 @@
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:38+00:00</t>
+          <t>2026-10-20T01:49:26+00:00</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
@@ -11183,7 +11183,7 @@
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:49+00:00</t>
+          <t>2026-10-20T01:49:37+00:00</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -11323,7 +11323,7 @@
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:15+00:00</t>
+          <t>2026-10-20T01:49:01+00:00</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
@@ -11463,7 +11463,7 @@
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:45+00:00</t>
+          <t>2026-10-20T01:49:33+00:00</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
@@ -11603,7 +11603,7 @@
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:21+00:00</t>
+          <t>2026-10-20T01:49:08+00:00</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
@@ -11742,7 +11742,7 @@
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:53+00:00</t>
+          <t>2026-10-20T01:49:40+00:00</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
@@ -11881,7 +11881,7 @@
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:26+00:00</t>
+          <t>2026-10-20T01:48:05+00:00</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -12023,7 +12023,7 @@
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:32+00:00</t>
+          <t>2026-10-20T01:48:09+00:00</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
@@ -12164,7 +12164,7 @@
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:43+00:00</t>
+          <t>2026-10-20T01:49:31+00:00</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
@@ -12300,7 +12300,7 @@
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:51+00:00</t>
+          <t>2026-10-20T01:49:39+00:00</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
@@ -12439,7 +12439,7 @@
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:23+00:00</t>
+          <t>2026-10-20T01:48:01+00:00</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
@@ -12568,7 +12568,7 @@
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:10+00:00</t>
+          <t>2026-10-20T01:47:47+00:00</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
@@ -12695,7 +12695,7 @@
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:44+00:00</t>
+          <t>2026-10-20T01:47:21+00:00</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -12829,7 +12829,7 @@
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:46+00:00</t>
+          <t>2026-10-20T01:47:23+00:00</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
@@ -12956,7 +12956,7 @@
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:57+00:00</t>
+          <t>2026-10-20T01:47:34+00:00</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
@@ -13096,7 +13096,7 @@
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:55+00:00</t>
+          <t>2026-10-20T01:49:43+00:00</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
@@ -13236,7 +13236,7 @@
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:32+00:00</t>
+          <t>2026-10-20T01:49:20+00:00</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
@@ -13371,7 +13371,7 @@
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:19+00:00</t>
+          <t>2026-10-20T01:49:08+00:00</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
@@ -13505,7 +13505,7 @@
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:50+00:00</t>
+          <t>2026-10-20T01:48:33+00:00</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
@@ -13634,7 +13634,7 @@
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:05+00:00</t>
+          <t>2026-10-20T01:46:47+00:00</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
@@ -13766,7 +13766,7 @@
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:07+00:00</t>
+          <t>2026-10-20T01:47:43+00:00</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
@@ -13888,7 +13888,7 @@
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:50+00:00</t>
+          <t>2026-10-20T01:47:27+00:00</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
@@ -14016,7 +14016,7 @@
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:05+00:00</t>
+          <t>2026-10-20T01:46:46+00:00</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
@@ -14142,7 +14142,7 @@
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:17+00:00</t>
+          <t>2026-10-20T01:46:58+00:00</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -14268,7 +14268,7 @@
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:19+00:00</t>
+          <t>2026-10-20T01:47:01+00:00</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
@@ -14394,7 +14394,7 @@
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:07+00:00</t>
+          <t>2026-10-20T01:46:49+00:00</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -14523,7 +14523,7 @@
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:35+00:00</t>
+          <t>2026-10-20T01:47:15+00:00</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
@@ -14651,7 +14651,7 @@
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:25+00:00</t>
+          <t>2026-10-20T01:47:05+00:00</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-19T20:45:00+00:00</t>
+          <t>2026-10-20T01:49:48+00:00</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
@@ -14928,7 +14928,7 @@
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:30+00:00</t>
+          <t>2026-10-20T01:49:18+00:00</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -15068,7 +15068,7 @@
       <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:53+00:00</t>
+          <t>2026-10-20T01:49:40+00:00</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
@@ -15208,7 +15208,7 @@
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:28+00:00</t>
+          <t>2026-10-20T01:49:16+00:00</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
@@ -15343,7 +15343,7 @@
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:42+00:00</t>
+          <t>2026-10-20T01:49:29+00:00</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
@@ -15482,7 +15482,7 @@
       <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:40+00:00</t>
+          <t>2026-10-20T01:49:27+00:00</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
@@ -15622,7 +15622,7 @@
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:36+00:00</t>
+          <t>2026-10-20T01:49:23+00:00</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
@@ -15766,7 +15766,7 @@
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:59+00:00</t>
+          <t>2026-10-20T01:48:45+00:00</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:15+00:00</t>
+          <t>2026-10-20T01:47:51+00:00</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
@@ -16023,7 +16023,7 @@
       <c r="Z115" t="inlineStr"/>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:39+00:00</t>
+          <t>2026-10-20T01:47:17+00:00</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
@@ -16151,7 +16151,7 @@
       <c r="Z116" t="inlineStr"/>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:11+00:00</t>
+          <t>2026-10-20T01:46:53+00:00</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
@@ -16290,7 +16290,7 @@
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:23+00:00</t>
+          <t>2026-10-20T01:49:11+00:00</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
@@ -16429,7 +16429,7 @@
       <c r="Z118" t="inlineStr"/>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:42+00:00</t>
+          <t>2026-10-20T01:48:23+00:00</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
@@ -16566,7 +16566,7 @@
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:53+00:00</t>
+          <t>2026-10-20T01:48:37+00:00</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
@@ -16706,7 +16706,7 @@
       <c r="Z120" t="inlineStr"/>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:00+00:00</t>
+          <t>2026-10-20T01:48:45+00:00</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
@@ -16848,7 +16848,7 @@
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:55+00:00</t>
+          <t>2026-10-20T01:48:38+00:00</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -16990,7 +16990,7 @@
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:57+00:00</t>
+          <t>2026-10-20T01:48:41+00:00</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
@@ -17131,7 +17131,7 @@
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:58+00:00</t>
+          <t>2026-10-20T01:48:42+00:00</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
@@ -17272,7 +17272,7 @@
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:54+00:00</t>
+          <t>2026-10-20T01:48:38+00:00</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
@@ -17409,7 +17409,7 @@
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:56+00:00</t>
+          <t>2026-10-20T01:48:41+00:00</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
@@ -17547,7 +17547,7 @@
       <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:52+00:00</t>
+          <t>2026-10-20T01:48:35+00:00</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
@@ -17679,7 +17679,7 @@
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:21+00:00</t>
+          <t>2026-10-20T01:47:01+00:00</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
@@ -17807,7 +17807,7 @@
       <c r="Z128" t="inlineStr"/>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:11+00:00</t>
+          <t>2026-10-20T01:47:50+00:00</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
@@ -17942,7 +17942,7 @@
       <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:04+00:00</t>
+          <t>2026-10-20T01:47:42+00:00</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
@@ -18076,7 +18076,7 @@
       <c r="Z130" t="inlineStr"/>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:04+00:00</t>
+          <t>2026-10-20T01:48:50+00:00</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -18218,7 +18218,7 @@
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:06+00:00</t>
+          <t>2026-10-20T01:48:53+00:00</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
@@ -18352,7 +18352,7 @@
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:28+00:00</t>
+          <t>2026-10-20T01:47:08+00:00</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
@@ -18481,7 +18481,7 @@
       <c r="Z133" t="inlineStr"/>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:36+00:00</t>
+          <t>2026-10-20T01:47:13+00:00</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
@@ -18607,7 +18607,7 @@
       <c r="Z134" t="inlineStr"/>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:17+00:00</t>
+          <t>2026-10-20T01:46:58+00:00</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
@@ -18737,7 +18737,7 @@
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:32+00:00</t>
+          <t>2026-10-20T01:47:12+00:00</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
@@ -18874,7 +18874,7 @@
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:03+00:00</t>
+          <t>2026-10-20T01:47:42+00:00</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
@@ -19006,7 +19006,7 @@
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:44+00:00</t>
+          <t>2026-10-20T01:47:23+00:00</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
@@ -19134,7 +19134,7 @@
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:48+00:00</t>
+          <t>2026-10-20T01:47:27+00:00</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
@@ -19260,7 +19260,7 @@
       <c r="Z139" t="inlineStr"/>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:40+00:00</t>
+          <t>2026-10-20T01:47:17+00:00</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
@@ -19388,7 +19388,7 @@
       <c r="Z140" t="inlineStr"/>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:36+00:00</t>
+          <t>2026-10-20T01:47:13+00:00</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
@@ -19514,7 +19514,7 @@
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:13+00:00</t>
+          <t>2026-10-20T01:46:54+00:00</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
@@ -19652,7 +19652,7 @@
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-19T20:42:03+00:00</t>
+          <t>2026-10-20T01:46:46+00:00</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
@@ -19774,7 +19774,7 @@
       <c r="Z143" t="inlineStr"/>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:15+00:00</t>
+          <t>2026-10-20T01:47:54+00:00</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
@@ -19915,7 +19915,7 @@
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:13+00:00</t>
+          <t>2026-10-20T01:49:01+00:00</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
@@ -20048,7 +20048,7 @@
       <c r="Z145" t="inlineStr"/>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-19T20:43:47+00:00</t>
+          <t>2026-10-20T01:48:29+00:00</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -20170,7 +20170,7 @@
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:26+00:00</t>
+          <t>2026-10-20T01:49:13+00:00</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
@@ -20309,7 +20309,7 @@
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:56+00:00</t>
+          <t>2026-10-20T01:49:44+00:00</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
@@ -20435,7 +20435,7 @@
       <c r="Z148" t="inlineStr"/>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:47+00:00</t>
+          <t>2026-10-20T01:49:35+00:00</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
@@ -20575,7 +20575,7 @@
       <c r="Z149" t="inlineStr"/>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-19T20:44:12+00:00</t>
+          <t>2026-10-20T01:49:00+00:00</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
@@ -40660,12 +40660,12 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Backorder</t>
         </is>
       </c>
       <c r="N269" t="n">

--- a/output/products.xlsx
+++ b/output/products.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB149"/>
+  <dimension ref="A1:AC149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,35 +525,40 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extra_specifications</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>image_urls</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>alternative_products</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>validation_status</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>validation_issues</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>scraped_at</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>content_hash</t>
         </is>
@@ -655,33 +660,38 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpaj.jpg</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:38+00:00</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>dea2498ec334784b</t>
+          <t>2026-10-20T04:51:12+00:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>a74ea92372a2f049</t>
         </is>
       </c>
     </row>
@@ -778,38 +788,43 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>{"Color": "Medical Blue", "Count Per Box": "200", "Material": "Nitrile"}</t>
+          <t>{"Color": "Medical blue", "Count Per Pack": "200", "Material": "Nitrile", "Product Type": "Dental exam gloves"}</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdk.jpg; https://www.safcodental.com/media/catalog/product/h/q/hqdefault_10_5.jpg</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:20+00:00</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>c8e6ba90859acd5a</t>
+          <t>2026-10-20T04:51:46+00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6063202603aec413</t>
         </is>
       </c>
     </row>
@@ -916,38 +931,43 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>{"Brand": "Alasta Aloe", "Color": "Cool Green", "Product Type": "Exam Gloves", "Skin Care Ingredient": "Certified Organic Aloe"}</t>
+          <t>{"Color": "Green"}</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcau.jpg</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN)</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:16+00:00</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2887a89083661c04</t>
+          <t>2026-10-20T04:51:42+00:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>c89bf18fa1c4c4f5</t>
         </is>
       </c>
     </row>
@@ -1054,38 +1074,43 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>{"Color": "Blue color", "Cuff Style": "Beaded cuff", "Finish": "Textured whole hand finish", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 1.2"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcan.jpg</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:01+00:00</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>4060a730f79a1564</t>
+          <t>2026-10-20T04:51:29+00:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>eb5bb3290a6f8229</t>
         </is>
       </c>
     </row>
@@ -1187,38 +1212,43 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>{"Color": "Pink", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Handedness": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam Gloves", "Texture": "Textured fingertip", "Thickness At Fingertips": "3.9 mils", "Thickness At Palm": "2.8 mils"}</t>
+          <t>{"Color": "Pink", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Intended Use": "Tested for use with chemotherapy drugs", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness At Fingertip": "3.9 mils", "Thickness At Palm": "2.8 mils"}</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccv.jpg</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Safco Nitrilex Black Gloves (DRCCX); Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:13+00:00</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>d2d6cb3d813a594a</t>
+          <t>2026-10-20T04:51:40+00:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1b38833cb0083638</t>
         </is>
       </c>
     </row>
@@ -1324,38 +1354,43 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Inner Coating": "Aloe", "Latex Protein Content": "50μg or less", "Material": "Latex", "Powder Status": "Powder-free", "Texture": "Textured"}</t>
+          <t>{"Coating": "Soothing aloe", "Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Latex exam gloves", "Texture": "Fully textured"}</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbad.jpg</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Durasoft Latex (DRBBK); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:28+00:00</t>
-        </is>
-      </c>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>269325beb9e54c69</t>
+          <t>2026-10-20T04:52:40+00:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3667091f1ec453f0</t>
         </is>
       </c>
     </row>
@@ -1465,38 +1500,43 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>{"Color": "Aqua", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
+          <t>{"Color": "Aqua", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured whole hand", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbl_2.jpg</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:49+00:00</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2f8987c5300856b2</t>
+          <t>2026-10-20T04:52:08+00:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6ed02127ecf9eca1</t>
         </is>
       </c>
     </row>
@@ -1605,38 +1645,43 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>{"Color": "Aqua blue", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8 mils; at fingertip3.5 mils; ±0.8"}</t>
+          <t>{"Color": "Aqua blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip3.5 mils; ±0.8"}</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdal_2.jpg</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL); Safco Nitrilex Black Gloves (DRCCX)</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:16+00:00</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>04745e2dee294084</t>
+          <t>2026-10-20T04:51:43+00:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>59c59052ba26799f</t>
         </is>
       </c>
     </row>
@@ -1746,38 +1791,43 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>{"Count Per Box": "300 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8mils; at fingertips 3.1 mils"}</t>
+          <t>{"Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8mils; at fingertips 3.1 mils"}</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbt.jpg</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:57+00:00</t>
-        </is>
-      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>55e74c1a301dd336</t>
+          <t>2026-10-20T04:51:27+00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>92bc5d268c71541c</t>
         </is>
       </c>
     </row>
@@ -1887,38 +1937,43 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Finish": "Black satin finish", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured full finger", "Thickness": "at palm 3.2 mils; at fingertip 4.0 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured full finger", "Thickness": "at palm 3.2 mils; at fingertip 4.0 mils"}</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcci.jpg</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:18+00:00</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>205b6900c7b9cb1d</t>
+          <t>2026-10-20T04:51:44+00:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>064bf3ce420f78b6</t>
         </is>
       </c>
     </row>
@@ -2028,38 +2083,43 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>{"Color": "Purple", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 3.0 mils"}</t>
+          <t>{"Color": "Purple", "Count Per Pack": "300 gloves per box (270 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 3.0 mils"}</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbm.jpg</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL); Safco Nitrilex Black Gloves (DRCCX)</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:57+00:00</t>
-        </is>
-      </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>aebf486aff3a9729</t>
+          <t>2026-10-20T04:51:26+00:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>c0c6cba04170af52</t>
         </is>
       </c>
     </row>
@@ -2170,38 +2230,43 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>{"Color": "Pink", "Cuff Style": "beaded", "Material": "nitrile", "Powder Status": "powder-free", "Quantity Per Box": "200 gloves", "Texture": "textured fingertip", "Thickness": "at palm 2.5 mils; at fingertips 2.7 mils"}</t>
+          <t>{"Color": "Pink", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertips 2.7 mils"}</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbu.jpg</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:08+00:00</t>
-        </is>
-      </c>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>aa56e5de71cf866d</t>
+          <t>2026-10-20T04:51:35+00:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>316a01c91862aecd</t>
         </is>
       </c>
     </row>
@@ -2305,38 +2370,43 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Fully-textured", "Thickness": "at palm 5.0 mils; at fingertips 6.0 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Fully-textured", "Thickness": "at palm 5.0 mils; at fingertips 6.0 mils"}</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccn.jpg</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Black Gloves (DRCCX); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL)</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:31+00:00</t>
-        </is>
-      </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>4b6d79d89e310eb1</t>
+          <t>2026-10-20T04:51:55+00:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>82a9a384ae6d862d</t>
         </is>
       </c>
     </row>
@@ -2445,38 +2515,43 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "100 gloves", "Cuff Style": "Beaded cuff", "Latex Protein Content": "50μg or less", "Texture": "Honeycomb textured fingertips and palms"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10", "Texture": "Honeycomb textured fingertips and palms"}</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/s/u/supermax-aurelia-distinct.jpg</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Durasoft Latex (DRBBK); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:27+00:00</t>
-        </is>
-      </c>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>c239464b4a98cc3a</t>
+          <t>2026-10-20T04:51:52+00:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3a026fdb2064c889</t>
         </is>
       </c>
     </row>
@@ -2585,38 +2660,43 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "100 gloves", "Cuff Type": "Beaded cuff", "Latex Protein Content": "50μg or less", "Texture": "Honeycomb textured fingertips and palms"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "100 gloves", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Texture": "Honeycomb textured fingertips and palms"}</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbao.jpg</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Durasoft Latex (DRBBK); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:19+00:00</t>
-        </is>
-      </c>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>68e9284463d8771d</t>
+          <t>2026-10-20T04:51:45+00:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>9c88238bbcf48b06</t>
         </is>
       </c>
     </row>
@@ -2726,38 +2806,43 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>{"Color": "Indigo blue", "Count Per Box": "100 gloves", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
+          <t>{"Color": "Indigo blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccl.jpg</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:23+00:00</t>
-        </is>
-      </c>
+      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>eafb2632c676ddba</t>
+          <t>2026-10-20T04:51:49+00:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>7239b5c593b319d3</t>
         </is>
       </c>
     </row>
@@ -2866,38 +2951,43 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Latex Protein Content": "50μg or less", "Material": "Latex", "Powder Status": "Powder-free", "Texture": "Micro-textured"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Latex exam gloves", "Texture": "Micro-textured"}</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbas.jpg</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:05+00:00</t>
-        </is>
-      </c>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>aa532d0374737a50</t>
+          <t>2026-10-20T04:51:33+00:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>7375eb993f5dbaaf</t>
         </is>
       </c>
     </row>
@@ -3006,38 +3096,43 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>{"Color": "Teal green", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Teal green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbf.jpg</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:22+00:00</t>
-        </is>
-      </c>
+      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>236d99a91cf842c2</t>
+          <t>2026-10-20T04:51:47+00:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>c6a3b4605a1ab2a2</t>
         </is>
       </c>
     </row>
@@ -3145,38 +3240,43 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip", "Thickness": "at palm 4.0 mils; at fingertip 5.2 mils; ± 1.2"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 4.0 mils; at fingertip 5.2 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcai.jpg</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:31+00:00</t>
-        </is>
-      </c>
+      <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>f1065b64a49a9a8f</t>
+          <t>2026-10-20T04:51:54+00:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>c1cad9bf24563bdd</t>
         </is>
       </c>
     </row>
@@ -3286,38 +3386,43 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>{"Color": "Indigo blue", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
+          <t>{"Color": "Indigo blue", "Count Per Pack": "300 gloves per box (270 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbw.jpg</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:11+00:00</t>
-        </is>
-      </c>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>4126b56ba7ca3c4a</t>
+          <t>2026-10-20T04:51:38+00:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>cb335e2f746c24bc</t>
         </is>
       </c>
     </row>
@@ -3426,38 +3531,43 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.0 mils; at fingertip 3.8 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.0 mils; at fingertip 3.8 mils"}</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbi.jpg</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:13+00:00</t>
-        </is>
-      </c>
+      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>cac6f42a2ce5dbcc</t>
+          <t>2026-10-20T04:51:39+00:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>c70e00eaae5db7d1</t>
         </is>
       </c>
     </row>
@@ -3563,29 +3673,34 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfsgl.jpg</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:31+00:00</t>
-        </is>
-      </c>
+      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>74621887c67e71db</t>
+          <t>2026-10-20T04:51:06+00:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>4e8a46dbb3549d2b</t>
         </is>
       </c>
     </row>
@@ -3695,38 +3810,43 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>{"Color": "Aqua", "Count Per Box": "300 gloves per box", "Cuff Style": "Beaded cuff", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
+          <t>{"Color": "Aqua", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcby.jpg</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:54+00:00</t>
-        </is>
-      </c>
+      <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>aa0e8b74b253e0f6</t>
+          <t>2026-10-20T04:52:13+00:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3460beb4eee3f3ef</t>
         </is>
       </c>
     </row>
@@ -3835,38 +3955,43 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Box": "100 gloves", "Cuff Style": "Beaded cuff", "Latex Protein Content": "50μg or less", "Texture": "Micro-textured whole hand finish"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Texture": "Micro-textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbbh.jpg</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex UltraSoft Gloves (DRCBN)</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:14+00:00</t>
-        </is>
-      </c>
+      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>aacba5e96c63f2d5</t>
+          <t>2026-10-20T04:52:29+00:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ad9830e581f443a0</t>
         </is>
       </c>
     </row>
@@ -3975,38 +4100,43 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>{"Boxes Per Case": "10 boxes", "Color": "Green", "Cuff Style": "Beaded cuff", "Material": "Chloroprene", "Powder Status": "Powder-free", "Quantity Per Box": "200 gloves per box", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils; ±0.2"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Chloroprene examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils; ±0.2"}</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdah.jpg</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL); Safco Nitrilex Black Gloves (DRCCX); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:34+00:00</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>3538b0290ffe781c</t>
+          <t>2026-10-20T04:51:57+00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>86b93e7a7fca3016</t>
         </is>
       </c>
     </row>
@@ -4114,38 +4244,43 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3 mils"}</t>
+          <t>{"Color": "White", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3 mils"}</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbd.jpg</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:22+00:00</t>
-        </is>
-      </c>
+      <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>79a7e1617db9e88e</t>
+          <t>2026-10-20T04:52:35+00:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>d2bf19f47334d16f</t>
         </is>
       </c>
     </row>
@@ -4255,38 +4390,43 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>{"Color": "Cobalt blue", "Count Per Box": "300 gloves", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 2.0 mils"}</t>
+          <t>{"Color": "Cobalt blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 2.0 mils"}</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbo.jpg</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:58+00:00</t>
-        </is>
-      </c>
+      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>422fbddd191b11d6</t>
+          <t>2026-10-20T04:51:28+00:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>e169b5970445974f</t>
         </is>
       </c>
     </row>
@@ -4394,38 +4534,43 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Texture": "Textured fingertip", "Thickness": "at palm 3 mils; at fingertip 4 mils; ± 0.8"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip", "Thickness": "at palm 3 mils; at fingertip 4 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcaz.jpg</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Safco Nitrilex Black Gloves (DRCCX); Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:09+00:00</t>
-        </is>
-      </c>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>8eed1bee892d036c</t>
+          <t>2026-10-20T04:51:36+00:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>fd11434fc73e9e9c</t>
         </is>
       </c>
     </row>
@@ -4534,38 +4679,43 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Cuff Style": "beaded cuff", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccw.jpg</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:54+00:00</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>45a60c804e7294f7</t>
+          <t>2026-10-20T04:51:25+00:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>df077f2a95c990e1</t>
         </is>
       </c>
     </row>
@@ -4668,38 +4818,43 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Cuff Style": "Beaded cuff", "Material": "Bio Nitrile", "Texture": "Textured fingertip finish", "Thickness At Fingertip": "2.2 mils", "Thickness At Palm": "2.0 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "300 gloves per box (250 size XL)", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness At Fingertip": "2.2 mils", "Thickness At Palm": "2.0 mils"}</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdg.jpg</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:57+00:00</t>
-        </is>
-      </c>
+      <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>5aead10f8ea6f935</t>
+          <t>2026-10-20T04:52:15+00:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>f53dc050b968c019</t>
         </is>
       </c>
     </row>
@@ -4802,38 +4957,43 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Cuff Style": "Beaded cuff", "Material": "nitrile", "Powder Status": "powder-free", "Product Type": "exam gloves", "Technology": "Glide Assist Technology", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
+          <t>{"Color": "Black", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdi.jpg</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:02+00:00</t>
-        </is>
-      </c>
+      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>a7e6ca2bcec68f80</t>
+          <t>2026-10-20T04:51:31+00:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ea74cad2190899cf</t>
         </is>
       </c>
     </row>
@@ -4942,38 +5102,43 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>{"Color": "Natural color", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Finish": "Textured whole hand finish"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbbe.jpg</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Durasoft Latex (DRBBK); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:36+00:00</t>
-        </is>
-      </c>
+      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>9ea71bf3396953d6</t>
+          <t>2026-10-20T04:52:46+00:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>71a8bda9f47fcc42</t>
         </is>
       </c>
     </row>
@@ -5082,38 +5247,43 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>{"Count Per Box": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0mils; at fingertips 2.7mils"}</t>
+          <t>{"Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0mils; at fingertips 2.7mils"}</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccy_2.jpg</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:14+00:00</t>
-        </is>
-      </c>
+      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>deafd0dabf3d7c93</t>
+          <t>2026-10-20T04:51:41+00:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>4c9d9ff22a856471</t>
         </is>
       </c>
     </row>
@@ -5220,38 +5390,43 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Cuff Style": "Beaded", "Fingertip Finish": "Textured", "Gloves per Box": "200", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils"}</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccg_2.jpg</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:49+00:00</t>
-        </is>
-      </c>
+      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>86550b4c5e67de1b</t>
+          <t>2026-10-20T04:52:09+00:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>58895b2b64d0e26d</t>
         </is>
       </c>
     </row>
@@ -5357,29 +5532,34 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfsjp.jpg</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:28+00:00</t>
-        </is>
-      </c>
+      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>111a3fb8989ff5a6</t>
+          <t>2026-10-20T04:51:04+00:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>e0408648d9c279de</t>
         </is>
       </c>
     </row>
@@ -5479,29 +5659,34 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfsmw.jpg</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr">
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:46+00:00</t>
-        </is>
-      </c>
+      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>074b051ef0c8d10d</t>
+          <t>2026-10-20T04:51:17+00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>e97a1fafe4ea3551</t>
         </is>
       </c>
     </row>
@@ -5611,33 +5796,38 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfvjj.jpg</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:20+00:00</t>
-        </is>
-      </c>
+      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>55db0280eb0da177</t>
+          <t>2026-10-20T04:50:57+00:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>3f84814a54864fee</t>
         </is>
       </c>
     </row>
@@ -5747,38 +5937,43 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>{"Collagen Type": "Type-I", "Material": "purified porcine Type-I peritoneum membrane", "Resorption Time": "16 weeks"}</t>
+          <t>{"Absorbability": "Fully absorbable", "Absorption Time": "16 weeks", "Intended Use": "osteogenesis during extraction socket preservation, ridge augmentation, periodontal defect repair or other grafting procedures", "Material": "Purified porcine Type-I peritoneum membrane", "Product Type": "Membrane"}</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwcc.jpg</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:50+00:00</t>
-        </is>
-      </c>
+      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>e3f6027ddd674b52</t>
+          <t>2026-10-20T04:50:34+00:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2903664669b50f40</t>
         </is>
       </c>
     </row>
@@ -5910,38 +6105,43 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>{"Available Sizes": "XS, S, M, L, XL", "Brand": "Cranberry® Compac", "Color": "Black", "Count Per Bag": "100 Gloves", "Material": "Powder-free nitrile", "Packaging": "100 gloves per bag", "Packaging Type": "Compact Polybag", "Product Type": "Nitrile Exam Gloves", "Sterility": "Non-sterile", "Texture": "Fingertip textured", "Thickness": "Approximately 2.2–2.5 mil", "Use Case": "Dental and clinical examination procedures"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100", "Intended Use": "Dental and clinical examination procedures", "Material": "Powder-free nitrile", "Packaging": "100 gloves per bag", "Powder Status": "Powder-free", "Product Type": "Nitrile Exam Gloves", "Sizes Available": "XS, S, M, L, XL", "Sterility": "Non-sterile", "Texture": "Fingertip textured", "Thickness": "Approximately 2.2–2.5 mil"}</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/c/r/cranberry-compac-nitrile-front-facing-100-box_1.jpg; https://www.safcodental.com/media/catalog/product/c/o/compac-nitrile-gloves-by-the-cuff-dispensing.jpg; https://www.safcodental.com/media/catalog/product/c/o/compac-nitrile-exam-gloves-by-the-cuff-dispensing-features.jpg</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex (DRCAL); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:26+00:00</t>
-        </is>
-      </c>
+      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>0e74594634840f0c</t>
+          <t>2026-10-20T04:51:50+00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>134f283d7122b758</t>
         </is>
       </c>
     </row>
@@ -6049,38 +6249,43 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "100 gloves", "Cuff Type": "Beaded", "Finish": "Textured whole hand", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100", "Cuff Style": "Beaded", "Packs Per Case": "10", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcaw_2.jpg</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:04+00:00</t>
-        </is>
-      </c>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>4879ee780bcf75f8</t>
+          <t>2026-10-20T04:52:20+00:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3da7b3acca9238a9</t>
         </is>
       </c>
     </row>
@@ -6184,42 +6389,47 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "100 gloves per box", "Cuff Type": "Beaded cuff", "Finish": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5 mils; ± 0.8"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcax_2.jpg</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>valid_with_warnings</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>missing_variants</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:12+00:00</t>
-        </is>
-      </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>bcecd9322146313f</t>
+          <t>2026-10-20T04:52:27+00:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3fafc4475cb125c2</t>
         </is>
       </c>
     </row>
@@ -6329,38 +6539,43 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Special Additives": "Lanolin and Vitamin E", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.5 mils; at fingertip 3.8 mils"}</t>
+          <t>{"Coating": "Lanolin and Vitamin E", "Color": "Blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam glove", "Texture": "Textured fingertip", "Thickness": "at palm 3.5 mils; at fingertip 3.8 mils"}</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcca_2.jpg</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:58+00:00</t>
-        </is>
-      </c>
+      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>a02f87a57cbe5211</t>
+          <t>2026-10-20T04:52:16+00:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>b7656234338a5733</t>
         </is>
       </c>
     </row>
@@ -6468,38 +6683,43 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Cuff Style": "Beaded", "Texture": "Textured", "Thickness": "at palm 3.5 mils; at fingertip 4 mils; ± 0.8"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves per box (50 left/right pairs)", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.5 mils; at fingertip 4 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcay_2.jpg</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:04+00:00</t>
-        </is>
-      </c>
+      <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>354cb9af412a03d5</t>
+          <t>2026-10-20T04:52:21+00:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>687c0f6935decc2a</t>
         </is>
       </c>
     </row>
@@ -6604,38 +6824,43 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>{"Color": "Wintergreen", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Latex Protein Content": "50μg or less", "Material": "Latex", "Powder Status": "Powder-free", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Color": "Wintergreen", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured"}</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbax_2.jpg</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Durasoft Latex (DRBBK); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:56+00:00</t>
-        </is>
-      </c>
+      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>6f561ceeeae68dd0</t>
+          <t>2026-10-20T04:52:14+00:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>a6f64f55ff28a1f7</t>
         </is>
       </c>
     </row>
@@ -6734,34 +6959,39 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>{"Form": "Dental Powder", "Material Type": "Cortical, Cancellous, Cortical/Cancellous Mix", "Sterility": "Sterile", "Sterilization Standard": "ISO 11137-2 Method 1"}</t>
+          <t>{"Form": "Ground", "Product Type": "Dental powder", "Standards": "ISO 11137-2 Method 1", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwvg.jpg</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr">
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:09+00:00</t>
-        </is>
-      </c>
+      <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>65c9a3bdc955dab5</t>
+          <t>2026-10-20T04:50:49+00:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1c9156efc3139ae0</t>
         </is>
       </c>
     </row>
@@ -6870,38 +7100,43 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>{"Boxes Per Case": "4", "Color": "Natural latex", "Count Per Box": "50 pairs (100 gloves)", "Cuff Type": "Beaded", "Length": "11.6\" (295mm)", "Material": "Latex", "Powder Status": "Powder-free", "Sterility": "Sterile", "Texture": "Textured", "Thickness": "at palm 7.5 mils; at fingertips: 8.0 mils"}</t>
+          <t>{"Color": "Natural latex color", "Cuff Style": "Beaded", "Length": "11.6\" (295mm)", "Material": "Latex", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured finish", "Thickness": "at palm 7.5 mils; at fingertips: 8.0 mils"}</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drecl.jpg</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex (DRCAL)</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:17+00:00</t>
-        </is>
-      </c>
+      <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>343e5d58cda9b809</t>
+          <t>2026-10-20T04:52:31+00:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>9931a24a25af8190</t>
         </is>
       </c>
     </row>
@@ -7007,29 +7242,34 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflse.jpg</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr">
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:34+00:00</t>
-        </is>
-      </c>
+      <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>6ff3ae25f0ff6607</t>
+          <t>2026-10-20T04:51:08+00:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>60c47c60c2316ea7</t>
         </is>
       </c>
     </row>
@@ -7135,38 +7375,43 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>{"Blade Material": "Stainless Steel", "Latex Status": "Not made with natural rubber latex", "Sterility": "Sterile"}</t>
+          <t>{"Intended Use": "tissue separation, and other procedures that require a sharp surgical blade to puncture or cut", "Latex Content": "Latex-free", "Material": "Stainless steel", "Product Type": "Disposable scalpel", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflug.jpg</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:39+00:00</t>
-        </is>
-      </c>
+      <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>8fb9be1e67961af3</t>
+          <t>2026-10-20T04:51:13+00:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>ea2bb6e6aea2a9fa</t>
         </is>
       </c>
     </row>
@@ -7272,29 +7517,34 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflun.jpg</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr">
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:36+00:00</t>
-        </is>
-      </c>
+      <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>f559e3be801c48f8</t>
+          <t>2026-10-20T04:51:10+00:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>8578b87d43dd84f6</t>
         </is>
       </c>
     </row>
@@ -7396,38 +7646,43 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>{"Boxes Per Case": "4 boxes in a case", "Color": "Natural latex color", "Count Per Box": "50 pairs (100 gloves) per box", "Cuff Type": "Beaded cuff", "Material": "Latex", "Powder Status": "Powder-free", "Sterility": "Sterile", "Texture": "Textured finish"}</t>
+          <t>{"Color": "Natural latex", "Count Per Pack": "50 pairs (100 gloves) per box", "Cuff Style": "Beaded", "Material": "Latex", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured"}</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drebh.jpg</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex (DRCAL); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:24+00:00</t>
-        </is>
-      </c>
+      <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>579346a035f20bc6</t>
+          <t>2026-10-20T04:52:37+00:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>dcb7f705b0ac83b1</t>
         </is>
       </c>
     </row>
@@ -7531,38 +7786,43 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>{"Available in 3 Sizes": "TPFS small , TPFM medium , TPFL large", "Case Pack": "100 gloves per box, 10 boxes per case", "Color": "Off White", "Fit": "Ambidextrous", "Latex": "Latex", "Length": "9.5\"", "Material": "Latex", "Powder Status": "Powder-free", "Product Name": "Essential Textured", "Texture": "Textured fingertips", "Thickness": "5.5 mil"}</t>
+          <t>{"Color": "Off White", "Count Per Pack": "100 gloves per box", "Fit": "Ambidextrous", "Length": "9.5\"", "Material": "Latex", "Packs Per Case": "100 gloves per box, 10 boxes per case", "Powder Status": "Powder-free", "Sizes Available": "TPFS small , TPFM medium , TPFL large", "Texture": "Textured fingertips", "Thickness": "5.5 mil"}</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbbp.jpg</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Durasoft Latex (DRBBK); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:08+00:00</t>
-        </is>
-      </c>
+      <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0409a00ecb6ce3e6</t>
+          <t>2026-10-20T04:52:25+00:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>4f70a243193a8eca</t>
         </is>
       </c>
     </row>
@@ -7663,38 +7923,43 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>{"Form": "Seamless swaging", "Texture": "Super-smooth", "Thickness": "micro-thin"}</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfehv.jpg</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>deterministic</t>
-        </is>
-      </c>
       <c r="Y53" t="inlineStr">
         <is>
+          <t>deterministic+llm</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:04+00:00</t>
-        </is>
-      </c>
+      <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>0805bf41b8b2c5ce</t>
+          <t>2026-10-20T04:50:45+00:00</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>61b268586ee7441c</t>
         </is>
       </c>
     </row>
@@ -7805,38 +8070,43 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>{"Color": "Royal blue", "Count Per Box": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.0 mils"}</t>
+          <t>{"Color": "Royal blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.0 mils"}</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbs_2.jpg</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:46+00:00</t>
-        </is>
-      </c>
+      <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>e108fcf150719916</t>
+          <t>2026-10-20T04:52:07+00:00</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>6ac724ce47fd0ce2</t>
         </is>
       </c>
     </row>
@@ -7944,33 +8214,38 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflvv.jpg</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:57+00:00</t>
-        </is>
-      </c>
+      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>bb5bd5db304cafd4</t>
+          <t>2026-10-20T04:50:38+00:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>358aad82addc83d2</t>
         </is>
       </c>
     </row>
@@ -8080,38 +8355,43 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Chloroprene", "Powder Status": "Powder-free", "Texture": "Fingertip textured", "Thickness": "at palm 3.0 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Fingertip textured", "Thickness": "at palm 3.0 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdai.jpg</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:20+00:00</t>
-        </is>
-      </c>
+      <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>c531563288876b03</t>
+          <t>2026-10-20T04:52:34+00:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>5897124ef17ec0e1</t>
         </is>
       </c>
     </row>
@@ -8215,38 +8495,43 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>{"Material": "collagen-based", "Packaging": "individually packaged", "Sterility": "sterile"}</t>
+          <t>{"Material": "Collagen-based", "Product Type": "Bone augmentation material", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfweg.jpg</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:50+00:00</t>
-        </is>
-      </c>
+      <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>e382042d859e438a</t>
+          <t>2026-10-20T04:50:33+00:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>6d7a26e9b43829ca</t>
         </is>
       </c>
     </row>
@@ -8353,38 +8638,43 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>{"Color": "Cobalt", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 1.9 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Cobalt", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 1.9 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdh.jpg</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Durasoft Latex (DRBBK); Safco Nitrilex Soothe (DRCDJ); Safco Nitrilex Black Gloves (DRCCX)</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:05+00:00</t>
-        </is>
-      </c>
+      <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>24de449dfa0e84b9</t>
+          <t>2026-10-20T04:51:34+00:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>a31002078a3096ac</t>
         </is>
       </c>
     </row>
@@ -8490,29 +8780,34 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwqj.jpg</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr">
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:19+00:00</t>
-        </is>
-      </c>
+      <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>63b2cb5ad20de1a4</t>
+          <t>2026-10-20T04:50:56+00:00</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>5de7e9330e91ea00</t>
         </is>
       </c>
     </row>
@@ -8615,38 +8910,43 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 3.5 mils; at fingertip 4.7 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.5 mils; at fingertip 4.7 mils"}</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbk.jpg</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:47+00:00</t>
-        </is>
-      </c>
+      <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>8f6c98e8504faf1c</t>
+          <t>2026-10-20T04:52:54+00:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5123adfb139d8ea8</t>
         </is>
       </c>
     </row>
@@ -8741,38 +9041,43 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Dispenser Type": "SMARTPULL* Dispenser", "Material": "Nitrile", "Quantity Per Box": "100 gloves", "Texture": "Textured fingertips"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100", "Material": "Nitrile", "Packaging": "SMARTPULL* Dispenser", "Product Type": "Exam Gloves", "Texture": "Textured fingertips"}</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdl.jpg</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:27+00:00</t>
-        </is>
-      </c>
+      <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>6cbbe85a5519b2b3</t>
+          <t>2026-10-20T04:51:51+00:00</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2f9634043b34c3b6</t>
         </is>
       </c>
     </row>
@@ -8886,38 +9191,43 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Fully absorbable", "Color": "White", "Packaging": "Individually packaged", "Product Type": "Collagen wound dressing", "Sterility": "Sterile", "Texture": "Porous, pliable"}</t>
+          <t>{"Absorbability": "Fully absorbable", "Color": "White", "Material": "Collagen", "Packaging": "Individually packaged", "Product Type": "Collagen wound dressing", "Sterility": "Sterile", "Texture": "Porous, pliable"}</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwqm.jpg</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:05+00:00</t>
-        </is>
-      </c>
+      <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>3b0342134662b039</t>
+          <t>2026-10-20T04:50:46+00:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>f5b6a58bac5ab522</t>
         </is>
       </c>
     </row>
@@ -9010,42 +9320,47 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>{"Material": "Purified bovine tendon", "Packaging": "Individually packed (1 per box)", "Properties": "Pliable; does not become slippery when hydrated", "Sterility": "Sterile"}</t>
+          <t>{"Absorbability": "Absorbable", "Count Per Pack": "1", "Intended Use": "guided tissue regeneration procedures in periodontal defects to enhance regeneration of the periodontal apparatus", "Material": "Purified bovine tendon", "Sterility": "Sterile", "Texture": "Pliable; does not become slippery when hydrated"}</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwqp.jpg</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>valid_with_warnings</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>missing_variants</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:49+00:00</t>
-        </is>
-      </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>450097604ecbe413</t>
+          <t>2026-10-20T04:51:21+00:00</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>d9dae4d74c7bfdf1</t>
         </is>
       </c>
     </row>
@@ -9146,38 +9461,43 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>{"Absorbability": "10 to 14 days", "Type": "Hemostatic"}</t>
+          <t>{"Absorption Time": "10 to 14 days", "Material": "Bovine tendon", "Product Type": "Hemostatic absorbable collagen material"}</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwqw.jpg</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:02+00:00</t>
-        </is>
-      </c>
+      <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>4127df710734d973</t>
+          <t>2026-10-20T04:50:43+00:00</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>e4b735a68ce342ef</t>
         </is>
       </c>
     </row>
@@ -9277,33 +9597,38 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpfp.jpg</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:30+00:00</t>
-        </is>
-      </c>
+      <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>e00d4173d5dc7561</t>
+          <t>2026-10-20T04:51:05+00:00</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>a540c286613db54b</t>
         </is>
       </c>
     </row>
@@ -9410,33 +9735,38 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/m/e/medicom-hemostat-20-box.jpg</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:54+00:00</t>
-        </is>
-      </c>
+      <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>59e296bcc51dfdc4</t>
+          <t>2026-10-20T04:50:36+00:00</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>7316e2997c19a832</t>
         </is>
       </c>
     </row>
@@ -9545,38 +9875,43 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>{"Color": "Lilac", "Count Per Box": "3 pairs", "Cuff Style": "Flat cuff", "Lining Type": "Flock-lined", "Material": "Nitrile", "Texture": "Textured whole hand finish", "Thickness": "0.38mm"}</t>
+          <t>{"Coating": "Flock-lined", "Color": "Lilac", "Count Per Pack": "3 pairs per box", "Cuff Style": "Flat", "Product Type": "Utility gloves", "Texture": "Textured whole hand finish", "Thickness": "0.38mm"}</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbg.jpg</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ); Safco Nitrilex Black Gloves (DRCCX)</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:32+00:00</t>
-        </is>
-      </c>
+      <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>911398137a5a63c1</t>
+          <t>2026-10-20T04:52:43+00:00</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>aff6cc2a8dddfe6f</t>
         </is>
       </c>
     </row>
@@ -9686,38 +10021,43 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>{"Color": "Aegean blue", "Count Per Box": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
+          <t>{"Color": "Aegean blue", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcch_2.jpg</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:53+00:00</t>
-        </is>
-      </c>
+      <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>1fe196809cc5fb88</t>
+          <t>2026-10-20T04:52:11+00:00</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>78b4fe61ad5fe2f3</t>
         </is>
       </c>
     </row>
@@ -9823,29 +10163,34 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfvgg.jpg</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr">
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:25+00:00</t>
-        </is>
-      </c>
+      <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>7ac8703d8d91fd7c</t>
+          <t>2026-10-20T04:51:01+00:00</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>b104b6e61b0f9900</t>
         </is>
       </c>
     </row>
@@ -9944,34 +10289,39 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>{"Absorption Time": "10 to 14 days", "Packaging": "Individually packaged", "Product Type": "Absorbable collagen wound dressing", "Sterility": "Sterile"}</t>
+          <t>{"Material": "Collagen", "Packaging": "Individually packaged", "Product Type": "Collagen wound dressing", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpfm.jpg</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr">
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:46+00:00</t>
-        </is>
-      </c>
+      <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>c0de206385850bd2</t>
+          <t>2026-10-20T04:51:18+00:00</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>0b51d35e026620dc</t>
         </is>
       </c>
     </row>
@@ -10066,34 +10416,39 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>{"DEHP Content": "Not made with DEHP", "Sterility": "Sterile", "Usage Duration": "24-hour"}</t>
+          <t>{"Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfxct.jpg</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr">
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:32+00:00</t>
-        </is>
-      </c>
+      <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>c35f16a1e9ef68b8</t>
+          <t>2026-10-20T04:51:07+00:00</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>f176b196082c5be6</t>
         </is>
       </c>
     </row>
@@ -10196,38 +10551,43 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>{"Latex": "Not manufactured with latex", "Port System": "Sturdy port system", "Pyrogen Status": "Nonpyrogenic", "Sterility": "Sterile"}</t>
+          <t>{"Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfxer.jpg</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:38+00:00</t>
-        </is>
-      </c>
+      <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>f76f78bec37310d8</t>
+          <t>2026-10-20T04:51:11+00:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>f771dca6ab2ff31e</t>
         </is>
       </c>
     </row>
@@ -10337,38 +10697,43 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>{"Color": "Lavender", "Count Per Box": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertips", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
+          <t>{"Color": "Lavender", "Count Per Pack": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertips", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcas.jpg</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:53+00:00</t>
-        </is>
-      </c>
+      <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>cc8b505a4c09e1e5</t>
+          <t>2026-10-20T04:51:24+00:00</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>35b8eac5eb378e2f</t>
         </is>
       </c>
     </row>
@@ -10469,38 +10834,43 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
+          <t>{"Standards": "ISO 9001"}</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfekr.jpg</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>deterministic</t>
-        </is>
-      </c>
       <c r="Y74" t="inlineStr">
         <is>
+          <t>deterministic+llm</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:09+00:00</t>
-        </is>
-      </c>
+      <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>e5c1242ca81fbf09</t>
+          <t>2026-10-20T04:50:48+00:00</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>aa8656caa4eaf516</t>
         </is>
       </c>
     </row>
@@ -10609,38 +10979,43 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>{"Color": "Azure blue", "Count Per Box": "300 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 2.6 mils"}</t>
+          <t>{"Color": "Azure blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 2.6 mils"}</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcck_2.jpg</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:05+00:00</t>
-        </is>
-      </c>
+      <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>0cf5aaa9d934fa75</t>
+          <t>2026-10-20T04:52:22+00:00</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>d217021b3be69a5d</t>
         </is>
       </c>
     </row>
@@ -10744,38 +11119,43 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>{"Boxes per Case": "10 boxes", "Color": "Blue", "Cuff Style": "Beaded cuff", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box (X-large 180 gloves per box)", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccz.jpg</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:47+00:00</t>
-        </is>
-      </c>
+      <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>56ec9806485b29cd</t>
+          <t>2026-10-20T04:52:55+00:00</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>54a61278da15d813</t>
         </is>
       </c>
     </row>
@@ -10877,38 +11257,43 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertips finish", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "200 gloves", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertips", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcap.jpg</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:44+00:00</t>
-        </is>
-      </c>
+      <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>a048cf5af2d74504</t>
+          <t>2026-10-20T04:52:52+00:00</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>8381cf6c54dd50f0</t>
         </is>
       </c>
     </row>
@@ -11018,38 +11403,43 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Neoprene (polychloroprene)", "Powder Status": "Powder-free", "Texture": "Textured fingertips", "Thickness": "at palm 5.1 mils; at fingertip 6.3 mils"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Neoprene (polychloroprene)", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertips", "Thickness": "at palm 5.1 mils; at fingertip 6.3 mils"}</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdag.jpg</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:26+00:00</t>
-        </is>
-      </c>
+      <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>e1b6a8786e321dfd</t>
+          <t>2026-10-20T04:52:38+00:00</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>888b079d18a5deb1</t>
         </is>
       </c>
     </row>
@@ -11157,38 +11547,43 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "beaded cuff", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "textured fingertip finish", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcct.jpg</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:37+00:00</t>
-        </is>
-      </c>
+      <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2bf928fc1b070e93</t>
+          <t>2026-10-20T04:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>074db92f980a3b47</t>
         </is>
       </c>
     </row>
@@ -11297,38 +11692,43 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Cuff Style": "Beaded", "Finish": "Textured whole hand finish", "Gloves per Box": "100", "Latex Protein Content": "50μg or less"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbai.jpg</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:01+00:00</t>
-        </is>
-      </c>
+      <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>9fdf6bb47f75f7fc</t>
+          <t>2026-10-20T04:52:19+00:00</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>81927d85be87ca5a</t>
         </is>
       </c>
     </row>
@@ -11437,38 +11837,43 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Material": "nitrile", "Powder Status": "Powder-free", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.7 mils; at fingertip 6.3 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.7 mils; at fingertip 6.3 mils"}</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbz.jpg</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:33+00:00</t>
-        </is>
-      </c>
+      <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>05d9c319740720fc</t>
+          <t>2026-10-20T04:52:44+00:00</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>0bdf713dfaa239d3</t>
         </is>
       </c>
     </row>
@@ -11577,38 +11982,43 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Box": "100 gloves", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdb.jpg</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:08+00:00</t>
-        </is>
-      </c>
+      <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>63b819e72b5b27b8</t>
+          <t>2026-10-20T04:52:24+00:00</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>c0e302964a92d9ad</t>
         </is>
       </c>
     </row>
@@ -11716,38 +12126,43 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.6 mils; at fingertip 3.7 mils"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100", "Cuff Style": "Beaded", "Packs Per Case": "10", "Texture": "Textured fingertip", "Thickness": "at palm 2.6 mils; at fingertip 3.7 mils"}</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcao.jpg</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:40+00:00</t>
-        </is>
-      </c>
+      <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>8f8a0c1b2a8971cf</t>
+          <t>2026-10-20T04:52:50+00:00</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>08e3fdfee505accb</t>
         </is>
       </c>
     </row>
@@ -11855,38 +12270,43 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded", "Packs Per Case": "10", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbc.jpg</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Soothe (DRCDJ); Safco Nitrilex UltraSoft Gloves (DRCBN)</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:05+00:00</t>
-        </is>
-      </c>
+      <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>395c49c36226887b</t>
+          <t>2026-10-20T04:51:32+00:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>fa36acf4d8879709</t>
         </is>
       </c>
     </row>
@@ -11997,38 +12417,43 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "100 gloves", "Cuff Style": "beaded", "Material": "chloroprene", "Powder Status": "powder-free", "Texture": "textured fingertip", "Thickness": "at palm 3.9 mils; at fingertip 5.1 mils"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.9 mils; at fingertip 5.1 mils"}</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdaf.jpg</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:09+00:00</t>
-        </is>
-      </c>
+      <c r="AA85" t="inlineStr"/>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>baf2cc50908f169d</t>
+          <t>2026-10-20T04:51:37+00:00</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>dda8b74944fd09a8</t>
         </is>
       </c>
     </row>
@@ -12138,38 +12563,43 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "100 gloves", "Cuff Style": "Beaded cuff", "Material": "Chloroprene", "Powder Status": "Powder-free", "Texture": "Textured whole hand finish", "Thickness": "at palm 5.1 mils; at fingertip 6.7 mils"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured whole hand", "Thickness": "at palm 5.1 mils; at fingertip 6.7 mils"}</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdac.jpg</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:31+00:00</t>
-        </is>
-      </c>
+      <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>095ac744f37cf75f</t>
+          <t>2026-10-20T04:52:42+00:00</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>6451d7e7fd9c0d77</t>
         </is>
       </c>
     </row>
@@ -12274,38 +12704,43 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Powder Status": "Powder-free", "Product Type": "Chloroprene examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdan.jpg</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:39+00:00</t>
-        </is>
-      </c>
+      <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>5e5a7de53333224c</t>
+          <t>2026-10-20T04:52:48+00:00</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>4705dd88561ff5db</t>
         </is>
       </c>
     </row>
@@ -12413,38 +12848,43 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>{"Color": "Cobalt blue", "Count Per Box": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Cobalt blue", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbj.jpg</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:01+00:00</t>
-        </is>
-      </c>
+      <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>868032d9cbf6cca5</t>
+          <t>2026-10-20T04:51:30+00:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>747f798fb02212fc</t>
         </is>
       </c>
     </row>
@@ -12547,33 +12987,38 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflqt.jpg</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:47+00:00</t>
-        </is>
-      </c>
+      <c r="AA89" t="inlineStr"/>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>e3490119f663b977</t>
+          <t>2026-10-20T04:51:19+00:00</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>651d099ad9d07744</t>
         </is>
       </c>
     </row>
@@ -12673,34 +13118,39 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>{"Sizes Available": "10-25", "Standards Compliance": "ISO-7740, ISO-13485"}</t>
+          <t>{"Product Type": "Surgical Blades", "Sizes Available": "10-25", "Standards": "ISO-7740, ISO-13485"}</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflwr.jpg</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr">
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:21+00:00</t>
-        </is>
-      </c>
+      <c r="AA90" t="inlineStr"/>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>ab3f3ee542036dca</t>
+          <t>2026-10-20T04:50:58+00:00</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>f8ca7225924e1d85</t>
         </is>
       </c>
     </row>
@@ -12803,38 +13253,43 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>{"Needle Coating": "RediPass", "Needle Material": "300 Series Stainless Steel", "Packaging": "Low-Memory Racetrack Tray", "Product Name": "RELI® PRO sutures", "Sterility": "Sterile", "Suture Type": "Absorbable and Non-Absorbable"}</t>
+          <t>{"Coating": "RediPass needle coating", "Material": "300 Series stainless steel", "Packaging": "Low-memory racetrack tray", "Product Type": "Surgical-grade sutures", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfelv.jpg</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:23+00:00</t>
-        </is>
-      </c>
+      <c r="AA91" t="inlineStr"/>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>724593b4ca939a23</t>
+          <t>2026-10-20T04:51:00+00:00</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>524acf02a642768f</t>
         </is>
       </c>
     </row>
@@ -12934,34 +13389,39 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>{"Shield Color": "Clear", "Shield Texture": "Non-slip"}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflxa.jpg</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>deterministic+llm</t>
-        </is>
-      </c>
+      <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr">
         <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:34+00:00</t>
-        </is>
-      </c>
+      <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>dc23cd99643487c0</t>
+          <t>2026-10-20T04:51:09+00:00</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>6eede0e878c531e6</t>
         </is>
       </c>
     </row>
@@ -13070,38 +13530,43 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 0.8"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcah.jpg</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:43+00:00</t>
-        </is>
-      </c>
+      <c r="AA93" t="inlineStr"/>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>f55e089f9c82183e</t>
+          <t>2026-10-20T04:52:51+00:00</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>7ffe8018cf438b24</t>
         </is>
       </c>
     </row>
@@ -13210,38 +13675,43 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "50 pairs (100 gloves) per box", "Count Per Case": "4 boxes in a case", "Cuff Style": "Beaded cuff", "Length": "12\"", "Material": "Nitrile", "Powder Status": "Powder-free", "Sterility": "Sterile", "Texture": "Textured finish", "Thickness at fingertips": "7.0 mils"}</t>
+          <t>{"Color": "White", "Count Per Pack": "50 pairs (100 gloves) per box", "Cuff Style": "Beaded", "Length": "12\"", "Material": "Nitrile", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured", "Thickness At Fingertip": "7.0 mils"}</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drecm.jpg</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:20+00:00</t>
-        </is>
-      </c>
+      <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>7259aae277ac0c21</t>
+          <t>2026-10-20T04:52:33+00:00</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>aae305130c1789a1</t>
         </is>
       </c>
     </row>
@@ -13345,38 +13815,43 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>{"Count Per Box": "100 Gloves", "Count Per Case": "10 Boxes", "Cuff Style": "Beaded Cuff", "Material": "Vinyl", "Powder Status": "Powder-free", "Product Type": "Examination Gloves", "Thickness": "at palm 3.2 mils; at fingertip 2.3 mils"}</t>
+          <t>{"Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Vinyl", "Packs Per Case": "10 boxes in a case", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Soft, form fitting", "Thickness": "at palm 3.2 mils; at fingertip 2.3 mils"}</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/druii_lc.jpg</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:08+00:00</t>
-        </is>
-      </c>
+      <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>d317fdf9ebe6ede4</t>
+          <t>2026-10-20T04:52:23+00:00</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>9b994fb1e1a51071</t>
         </is>
       </c>
     </row>
@@ -13479,38 +13954,43 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>{"Color": "Emerald green", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Powder Status": "Powder-free", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.1 mils; at fingertip 4 mils", "Type": "Examination gloves"}</t>
+          <t>{"Color": "Emerald green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.1 mils; at fingertip 4 mils"}</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdas.jpg</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:33+00:00</t>
-        </is>
-      </c>
+      <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>054d1196891f335f</t>
+          <t>2026-10-20T04:51:56+00:00</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>8bb635a37f6549d2</t>
         </is>
       </c>
     </row>
@@ -13617,29 +14097,34 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpgh.jpg; https://www.safcodental.com/media/catalog/product/s/e/septodont-orasoothe-oral-coating-rinse-hygiene-3-4-oz_1.jpg</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr">
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:47+00:00</t>
-        </is>
-      </c>
+      <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11018d593b020d07</t>
+          <t>2026-10-20T04:50:31+00:00</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>203a0886af81d89e</t>
         </is>
       </c>
     </row>
@@ -13740,38 +14225,43 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>{"Form": "Cubes", "Intended Use": "Dental surgical procedures", "Packaging": "Individually packaged", "Resorption Time": "3-7 days", "Standard": "USP", "Sterility": "Sterile", "Type": "Absorbable gelatin sponge hemostat"}</t>
+          <t>{"Absorption Capacity": "35x its weight", "Absorption Time": "3-7 days", "Form": "Cubes", "Packaging": "Individually packaged", "Product Type": "Absorbable gelatin sponge hemostat", "Standards": "USP", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpfs.jpg</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:43+00:00</t>
-        </is>
-      </c>
+      <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>1d95abd2c10ba9a9</t>
+          <t>2026-10-20T04:51:16+00:00</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>523b234884c4d821</t>
         </is>
       </c>
     </row>
@@ -13871,29 +14361,34 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpfq.jpg</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr">
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:27+00:00</t>
-        </is>
-      </c>
+      <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>e53601900cbc21b9</t>
+          <t>2026-10-20T04:51:03+00:00</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>47fce997d059015e</t>
         </is>
       </c>
     </row>
@@ -13990,38 +14485,43 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>{"Packaging Type": "Jars", "Sterility": "Double-sterile"}</t>
+          <t>{"Packaging": "Jars", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrd.jpg</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:46+00:00</t>
-        </is>
-      </c>
+      <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>e8e695083cec5bce</t>
+          <t>2026-10-20T04:50:30+00:00</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>411e2ded0fb3131f</t>
         </is>
       </c>
     </row>
@@ -14121,33 +14621,38 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrg.jpg</t>
         </is>
       </c>
-      <c r="W101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:58+00:00</t>
-        </is>
-      </c>
+      <c r="AA101" t="inlineStr"/>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>364be970049c1b5f</t>
+          <t>2026-10-20T04:50:40+00:00</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>85756c5d0ef7f76b</t>
         </is>
       </c>
     </row>
@@ -14247,33 +14752,38 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrf.jpg</t>
         </is>
       </c>
-      <c r="W102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:01+00:00</t>
-        </is>
-      </c>
+      <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>f040300769da78de</t>
+          <t>2026-10-20T04:50:41+00:00</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>f63a59f225d4ff1e</t>
         </is>
       </c>
     </row>
@@ -14368,38 +14878,43 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>{"Demineralized Bone Content": "30%", "Mineralized Bone Content": "70%", "Particle Size": "0.5 – 1.0mm"}</t>
+          <t>{"Particle Size": "0.5 – 1.0mm"}</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwre.jpg</t>
         </is>
       </c>
-      <c r="W103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:49+00:00</t>
-        </is>
-      </c>
+      <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15f4f9e1d1f155aa</t>
+          <t>2026-10-20T04:50:32+00:00</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>ee3b4e0b24664a68</t>
         </is>
       </c>
     </row>
@@ -14506,29 +15021,34 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpfr.jpg</t>
         </is>
       </c>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr">
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:15+00:00</t>
-        </is>
-      </c>
+      <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>879e914d77cf6e5a</t>
+          <t>2026-10-20T04:50:53+00:00</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>0bdc0152695b68f0</t>
         </is>
       </c>
     </row>
@@ -14634,29 +15154,34 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfedb.jpg</t>
         </is>
       </c>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr">
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:05+00:00</t>
-        </is>
-      </c>
+      <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>7e880dfe44c361b8</t>
+          <t>2026-10-20T04:50:44+00:00</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>8f1f61222a7a24ad</t>
         </is>
       </c>
     </row>
@@ -14755,42 +15280,47 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>{"Color": "Natural white", "Cuff Style": "Beaded cuff", "Gloves per Box": "100", "Layer Count": "Multi-layer", "Material": "Latex", "Powder Status": "Powder-free", "Product Type": "Exam Gloves", "Texture": "Textured fingertip"}</t>
+          <t>{"Color": "Natural white", "Count Per Pack": "100", "Cuff Style": "Beaded", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip"}</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbbl.jpg</t>
         </is>
       </c>
-      <c r="W106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex (DRCAL); Safco Durasoft Latex (DRBBK); Safco Nitrilex Surpass Gloves (DRCCS)</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>valid_with_warnings</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
+      <c r="AA106" t="inlineStr">
         <is>
           <t>missing_variants</t>
         </is>
       </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:48+00:00</t>
-        </is>
-      </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>6287905efdcbc290</t>
+          <t>2026-10-20T04:52:56+00:00</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>0bb8c1b6df5d1424</t>
         </is>
       </c>
     </row>
@@ -14902,38 +15432,43 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>{"AQL": "1.5", "Color": "Black", "Count Per Box": "100 gloves", "Cuff Style": "beaded cuff", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "Fully textured", "Thickness": "5.0 mil"}</t>
+          <t>{"AQL": "1.5", "Color": "Black", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Fully textured", "Thickness": "5.0 mil"}</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdd.jpg</t>
         </is>
       </c>
-      <c r="W107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:18+00:00</t>
-        </is>
-      </c>
+      <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>6e9feb3b30524b10</t>
+          <t>2026-10-20T04:52:32+00:00</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>75ca628579679d1a</t>
         </is>
       </c>
     </row>
@@ -15042,38 +15577,43 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Box": "100 gloves", "Cuff Style": "Beaded cuff", "Material": "Latex", "Powder Status": "Powder-free", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbbm.jpg</t>
         </is>
       </c>
-      <c r="W108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:40+00:00</t>
-        </is>
-      </c>
+      <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>07d81972770971cc</t>
+          <t>2026-10-20T04:52:49+00:00</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>cfcf1f6033c4b4e1</t>
         </is>
       </c>
     </row>
@@ -15182,38 +15722,43 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>{"Color": "Dark lavender blue", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.0mils; at fingertips 3.5 mils"}</t>
+          <t>{"Color": "Dark lavender blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.0mils; at fingertips 3.5 mils"}</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbq.jpg</t>
         </is>
       </c>
-      <c r="W109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:16+00:00</t>
-        </is>
-      </c>
+      <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>a397bc377c579618</t>
+          <t>2026-10-20T04:52:30+00:00</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>171fa39f4bb61820</t>
         </is>
       </c>
     </row>
@@ -15317,38 +15862,43 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>{"Boxes Per Case": "10 boxes in a case", "Color": "Blue", "Count Per Box": "300 gloves per box", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.0 mils."}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.0 mils."}</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccf.jpg</t>
         </is>
       </c>
-      <c r="W110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:29+00:00</t>
-        </is>
-      </c>
+      <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>77b9ec6bdf270ef1</t>
+          <t>2026-10-20T04:52:41+00:00</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>54b6652cac118553</t>
         </is>
       </c>
     </row>
@@ -15456,38 +16006,43 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Cuff Type": "Beaded", "Gloves Per Box": "100", "Latex Protein Content": "50μg or less", "Texture": "Textured"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Texture": "Textured"}</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbav.jpg</t>
         </is>
       </c>
-      <c r="W111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex (DRCAL); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex UltraSoft Gloves (DRCBN)</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:27+00:00</t>
-        </is>
-      </c>
+      <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>8e1b2a6410d1a768</t>
+          <t>2026-10-20T04:52:39+00:00</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>d19b823764ec6346</t>
         </is>
       </c>
     </row>
@@ -15596,38 +16151,43 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>{"Color": "purple", "Count Per Pack": "100 gloves per box", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "textured fingertip", "Thickness": "at palm 4.7 mils; at fingertip 5.9 mils", "Type": "exam gloves"}</t>
+          <t>{"Color": "Purple", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 4.7 mils; at fingertip 5.9 mils"}</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcab.jpg</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:23+00:00</t>
-        </is>
-      </c>
+      <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>3dab2dd7de46c431</t>
+          <t>2026-10-20T04:52:36+00:00</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>cf37adf9200ed510</t>
         </is>
       </c>
     </row>
@@ -15740,38 +16300,43 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>{"Case Pack": "100 gloves per box, 10 boxes per case", "Color": "Vibrant blue", "Cuff Style": "Beaded cuff", "Fit": "Ambidextrous", "Glove Type": "exam gloves", "Industries": "Dental, veterinarian, mortuary, cleaning, tattoo", "Length": "9.5\"", "Material": "nitrile", "Powder Status": "powder-free", "Surface Texture": "Micro-textured outer surface", "Thickness": "4.0 MIL"}</t>
+          <t>{"Color": "Vibrant blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Intended Use": "Dental, veterinarian, mortuary, cleaning, tattoo", "Length": "9.5\"", "Material": "Nitrile", "Packs Per Case": "100 gloves per box, 10 boxes per case", "Powder Status": "Powder-free", "Texture": "Micro-textured outer surface", "Thickness": "4.0 MIL"}</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcde.jpg</t>
         </is>
       </c>
-      <c r="W113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:45+00:00</t>
-        </is>
-      </c>
+      <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>9a5665ec9b835b28</t>
+          <t>2026-10-20T04:52:05+00:00</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>c371723e102bca40</t>
         </is>
       </c>
     </row>
@@ -15866,38 +16431,43 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>{"Absorbability": "4-8 weeks", "Customizable": "Cut to size and shape"}</t>
+          <t>{"Absorbability": "Absorbable", "Absorption Time": "4-8 weeks", "Form": "Cut to size and shape", "Intended Use": "barrier to protect PDL development from fast growing tissues"}</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrx.jpg</t>
         </is>
       </c>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr">
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>valid_with_warnings</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>missing_variants</t>
         </is>
       </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:51+00:00</t>
-        </is>
-      </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>ec1fa004da37d33a</t>
+          <t>2026-10-20T04:51:22+00:00</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>a951ea12082753ce</t>
         </is>
       </c>
     </row>
@@ -16001,34 +16571,39 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>{"Indications include": "post-extraction socket preservation, periodontal defects, infrabony defects, peri-implant defects, sinus lift, ridge augmentation, and cystic cavities.", "Material Composition": "Biphasic β-TCP (β-Tricalcium phosphate) / Hydroxyapatite", "Product Type": "Synthetic bone grafting material", "Resorbability": "Fully resorbable", "Sterility": "Sterile"}</t>
+          <t>{"Absorbability": "Fully resorbable", "Intended Use": "post-extraction socket preservation, periodontal defects, infrabony defects, peri-implant defects, sinus lift, ridge augmentation, and cystic cavities.", "Material": "Biphasic β-TCP (β-Tricalcium phosphate) / Hydroxyapatite", "Product Type": "Synthetic bone grafting material", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwru.jpg</t>
         </is>
       </c>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr">
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:17+00:00</t>
-        </is>
-      </c>
+      <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>b8e56554b64417b3</t>
+          <t>2026-10-20T04:50:54+00:00</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>e762674e22cda8a1</t>
         </is>
       </c>
     </row>
@@ -16130,33 +16705,38 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrl.jpg</t>
         </is>
       </c>
-      <c r="W116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:53+00:00</t>
-        </is>
-      </c>
+      <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>90955aa05269edf3</t>
+          <t>2026-10-20T04:50:35+00:00</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>da2bfcba1cd9d1cb</t>
         </is>
       </c>
     </row>
@@ -16264,38 +16844,43 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>{"Color": "Dark blue", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
+          <t>{"Color": "Dark blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbx_2.jpg</t>
         </is>
       </c>
-      <c r="W117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:11+00:00</t>
-        </is>
-      </c>
+      <c r="AA117" t="inlineStr"/>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>3ee97abfead19f0d</t>
+          <t>2026-10-20T04:52:26+00:00</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>d90b26a9114e14df</t>
         </is>
       </c>
     </row>
@@ -16403,38 +16988,43 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccr_2.jpg</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:23+00:00</t>
-        </is>
-      </c>
+      <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>7112087d457a8aad</t>
+          <t>2026-10-20T04:51:48+00:00</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>b4a3eba4eac589c0</t>
         </is>
       </c>
     </row>
@@ -16544,34 +17134,39 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>{"Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Powder Status": "Powder-free", "Product Type": "Latex exam gloves", "Protein Content": "50μg or less", "Texture": "Whole-hand micro-textured finish"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Natural latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Micro-textured"}</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbbk.jpg</t>
         </is>
       </c>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr">
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:37+00:00</t>
-        </is>
-      </c>
+      <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>3d4f3d507423a2b5</t>
+          <t>2026-10-20T04:51:59+00:00</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>d1266b547214d4cb</t>
         </is>
       </c>
     </row>
@@ -16680,38 +17275,43 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 3.0 mils; at fingertips 3.5 mils", "Type": "Examination"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Powder Status": "Powder-free", "Product Type": "Chloroprene examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.0 mils; at fingertips 3.5 mils"}</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdap.jpg</t>
         </is>
       </c>
-      <c r="W120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex Soothe (DRCDJ); Safco Nitrilex Black Gloves (DRCCX)</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:45+00:00</t>
-        </is>
-      </c>
+      <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>f221b09740cda446</t>
+          <t>2026-10-20T04:52:06+00:00</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>c1baa629eaa1742d</t>
         </is>
       </c>
     </row>
@@ -16822,38 +17422,43 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Box": "200 gloves", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Powder-free nitrile exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccx.jpg</t>
         </is>
       </c>
-      <c r="W121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>Safco Nitrilex Soothe (DRCDJ); Safco Durasoft Latex (DRBBK)</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="Y121" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:38+00:00</t>
-        </is>
-      </c>
+      <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>af76593a44d16fb4</t>
+          <t>2026-10-20T04:52:01+00:00</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>3244e07d4f08f48d</t>
         </is>
       </c>
     </row>
@@ -16964,38 +17569,43 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "300 gloves per box", "Cuff Style": "Beaded cuff", "Material": "nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip finish", "Thickness At Fingertips": "3.0 mils", "Thickness At Palm": "2.5 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness At Fingertip": "3.0 mils", "Thickness At Palm": "2.5 mils"}</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccj.jpg</t>
         </is>
       </c>
-      <c r="W122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="Y122" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:41+00:00</t>
-        </is>
-      </c>
+      <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>79a6f62dc9b9c9ce</t>
+          <t>2026-10-20T04:52:03+00:00</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>ff94ed1850bfc8bc</t>
         </is>
       </c>
     </row>
@@ -17105,38 +17715,43 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Micro-textured", "Texture Finish": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcal.jpg</t>
         </is>
       </c>
-      <c r="W123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Black Gloves (DRCCX)</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="Y123" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:42+00:00</t>
-        </is>
-      </c>
+      <c r="AA123" t="inlineStr"/>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>dba6beb1036bda26</t>
+          <t>2026-10-20T04:52:04+00:00</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>88924b13592b1f60</t>
         </is>
       </c>
     </row>
@@ -17246,38 +17861,43 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>{"Color": "Lavender blue", "Count Per Box": "200 gloves per box", "Cuff Style": "Beaded cuff", "Dispensing": "One by one", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 3.2 mils; at fingertips 3.5 mils"}</t>
+          <t>{"Color": "Lavender blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.2 mils; at fingertips 3.5 mils"}</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcbn.jpg</t>
         </is>
       </c>
-      <c r="W124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>Safco Nitrilex Black Gloves (DRCCX); Safco Durasoft Latex (DRBBK); Safco Nitrilex Soothe (DRCDJ)</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="Y124" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:38+00:00</t>
-        </is>
-      </c>
+      <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>94bf0a18bcfe008d</t>
+          <t>2026-10-20T04:52:00+00:00</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>b0bcfa821478fd28</t>
         </is>
       </c>
     </row>
@@ -17383,38 +18003,43 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>{"Coating": "Colloidal Oatmeal", "Color": "Robin Egg Blue", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Testing Standard": "Chemotherapy drug tested per ASTM D6978", "Texture": "Textured Fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.3 mils", "Type": "Exam Gloves"}</t>
+          <t>{"Coating": "Colloidal oatmeal", "Color": "Robin Egg Blue", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Standards": "Chemotherapy drug tested per ASTM D6978", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.3 mils"}</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdj.jpg</t>
         </is>
       </c>
-      <c r="W125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:41+00:00</t>
-        </is>
-      </c>
+      <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>0c77277726be5d3e</t>
+          <t>2026-10-20T04:52:02+00:00</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>2b3ef70260916870</t>
         </is>
       </c>
     </row>
@@ -17525,34 +18150,39 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>{"Chemotherapy Approval": "ASTM D6978 tested and approved", "Color": "Blue", "Count Per Box": "300 gloves per box", "Cuff Style": "Beaded cuff", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertips", "Texture Finish": "Textured fingertip finish", "Thickness": "at palm 3.2 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "300 gloves", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Standards": "ASTM D6978", "Thickness": "at palm 3.2 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccs.jpg</t>
         </is>
       </c>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr">
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:35+00:00</t>
-        </is>
-      </c>
+      <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>de07e78fcc342907</t>
+          <t>2026-10-20T04:51:58+00:00</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>f78b674159b13d91</t>
         </is>
       </c>
     </row>
@@ -17657,34 +18287,39 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Non-absorbable", "Chromic gut (catgut)": "Produced with the same precision and quality materials as plain gut, plus treated with chromic acid salts to decrease tissue reactivity and provide a slower absorption rate.", "Color": "Black", "Plain gut (catgut)": "Made of first quality raw material, catgut has extremely high tensile strength. Every strand is precision polished to a uniform diameter, permitting smooth and secure knotting.", "Structure": "Monofilament"}</t>
+          <t>{"Absorbability": "Non-absorbable", "Color": "Black", "Form": "Monofilament", "Product Type": "Suture"}</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
+          <t>{"Chromic gut (catgut)": "Produced with the same precision and quality materials as plain gut, plus treated with chromic acid salts to decrease tissue reactivity and provide a slower absorption rate.", "Plain gut (catgut)": "Made of first quality raw material, catgut has extremely high tensile strength. Every strand is precision polished to a uniform diameter, permitting smooth and secure knotting."}</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfemn.jpg</t>
         </is>
       </c>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr">
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:01+00:00</t>
-        </is>
-      </c>
+      <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2a90ff3dedbb6113</t>
+          <t>2026-10-20T04:50:42+00:00</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>0118fb78c0c5cfa9</t>
         </is>
       </c>
     </row>
@@ -17790,29 +18425,34 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflvz.jpg</t>
         </is>
       </c>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr">
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:50+00:00</t>
-        </is>
-      </c>
+      <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>f2d9895c06ce5bdc</t>
+          <t>2026-10-20T04:51:20+00:00</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>e8a89720a6f2c659</t>
         </is>
       </c>
     </row>
@@ -17916,38 +18556,43 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>{"Handle Style": "#3", "Intended Area": "Posterior and palatal areas", "Intended Use": "Cutting gingival tissue and making surgical incisions", "Special Feature": "Metric Ruler"}</t>
+          <t>{"Form": "European Round", "Intended Use": "cutting gingival tissue and making surgical incisions", "Product Type": "Scalpel handle"}</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
+          <t>{"Features": "metric ruler"}</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflnb.jpg</t>
         </is>
       </c>
-      <c r="W129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="Y129" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:42+00:00</t>
-        </is>
-      </c>
+      <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>9f02a5ff2f1e3250</t>
+          <t>2026-10-20T04:51:15+00:00</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>23379befd492fe78</t>
         </is>
       </c>
     </row>
@@ -18050,38 +18695,43 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Cuff Style": "Beaded cuff", "Finish": "Textured whole hand finish", "Gloves Per Box": "100", "Latex Protein Content": "50µg or less"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50µg or less", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbar_2.jpg</t>
         </is>
       </c>
-      <c r="W130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:50+00:00</t>
-        </is>
-      </c>
+      <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>d3035144e3dd7fe9</t>
+          <t>2026-10-20T04:52:10+00:00</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>043167d279a4019a</t>
         </is>
       </c>
     </row>
@@ -18192,38 +18842,43 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>{"Color": "natural", "Count Per Box": "100 gloves", "Cuff Style": "beaded", "Latex Protein Content": "50μg or less", "Material": "latex", "Powder Status": "powder-free", "Texture": "textured whole hand finish"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand"}</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbac_2.jpg</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Durasoft Latex (DRBBK); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X131" t="inlineStr">
+      <c r="Y131" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y131" t="inlineStr">
+      <c r="Z131" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr"/>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:53+00:00</t>
-        </is>
-      </c>
+      <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>218ffda28962c608</t>
+          <t>2026-10-20T04:52:12+00:00</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>14e6cb47a3ef865e</t>
         </is>
       </c>
     </row>
@@ -18330,34 +18985,39 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
+          <t>{"Form": "IV bags", "Material": "Not manufactured with latex, PVC or DEHP"}</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr">
+      <c r="W132" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfxhj.jpg</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>deterministic</t>
-        </is>
-      </c>
+      <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr">
         <is>
+          <t>deterministic+llm</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:08+00:00</t>
-        </is>
-      </c>
+      <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>aa8bed6751eccbab</t>
+          <t>2026-10-20T04:50:47+00:00</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>7567137ae403d4b7</t>
         </is>
       </c>
     </row>
@@ -18464,29 +19124,34 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfxhk.jpg</t>
         </is>
       </c>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr">
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y133" t="inlineStr">
+      <c r="Z133" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:13+00:00</t>
-        </is>
-      </c>
+      <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>8d0e8631a897bf28</t>
+          <t>2026-10-20T04:50:52+00:00</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>3a6e75b0aed4f099</t>
         </is>
       </c>
     </row>
@@ -18586,33 +19251,38 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflwh.jpg</t>
         </is>
       </c>
-      <c r="W134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
+      <c r="Y134" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:58+00:00</t>
-        </is>
-      </c>
+      <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>507e2e3b64377294</t>
+          <t>2026-10-20T04:50:39+00:00</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>68b440e2fce1d69c</t>
         </is>
       </c>
     </row>
@@ -18715,34 +19385,39 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>{"Pyrogen Status": "Nonpyrogenic", "Sterility": "Sterile", "Tonicity": "Hypotonic"}</t>
+          <t>{"Coating": "Contains no bacteriostatic or antimicrobial agents", "Form": "IV bags", "Latex Content": "not manufactured with latex", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
+          <t>{"Pyrogen Status": "nonpyrogenic"}</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfxkq.jpg</t>
         </is>
       </c>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr">
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Z135" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:12+00:00</t>
-        </is>
-      </c>
+      <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>59930b1e0bfb3a5f</t>
+          <t>2026-10-20T04:50:50+00:00</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>3f335619253ec134</t>
         </is>
       </c>
     </row>
@@ -18848,38 +19523,43 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>{"Handle Size 3 Compatible Blades": "10-15", "Handle Size 4 Compatible Blades": "20-25"}</t>
+          <t>{"Sizes Available": "3, 4"}</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflma.jpg</t>
         </is>
       </c>
-      <c r="W136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
+      <c r="Y136" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="Z136" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:42+00:00</t>
-        </is>
-      </c>
+      <c r="AA136" t="inlineStr"/>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>44b1cc0dfac82ad9</t>
+          <t>2026-10-20T04:51:14+00:00</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>6d14b366eaa1c123</t>
         </is>
       </c>
     </row>
@@ -18985,33 +19665,38 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfljq.jpg</t>
         </is>
       </c>
-      <c r="W137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X137" t="inlineStr">
+      <c r="Y137" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="Z137" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:23+00:00</t>
-        </is>
-      </c>
+      <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>558a5436394ea8b9</t>
+          <t>2026-10-20T04:50:59+00:00</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>86b00bde719ef60e</t>
         </is>
       </c>
     </row>
@@ -19117,29 +19802,34 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfldb.jpg</t>
         </is>
       </c>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr">
+      <c r="X138" t="inlineStr"/>
+      <c r="Y138" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:27+00:00</t>
-        </is>
-      </c>
+      <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>8f38e2131a276c7c</t>
+          <t>2026-10-20T04:51:02+00:00</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>caded21b9bec16d3</t>
         </is>
       </c>
     </row>
@@ -19239,33 +19929,38 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflta.jpg</t>
         </is>
       </c>
-      <c r="W139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
+      <c r="Y139" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:17+00:00</t>
-        </is>
-      </c>
+      <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>1a30c11383647598</t>
+          <t>2026-10-20T04:50:55+00:00</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>78707d036fff6cb5</t>
         </is>
       </c>
     </row>
@@ -19371,29 +20066,34 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflgv.jpg</t>
         </is>
       </c>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr">
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:13+00:00</t>
-        </is>
-      </c>
+      <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>d31953cea06a3193</t>
+          <t>2026-10-20T04:50:51+00:00</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>18324d4067f6b55f</t>
         </is>
       </c>
     </row>
@@ -19488,38 +20188,43 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>{"Absorbability Timeframe": "Within 7-14 days", "Product Type": "Absorbable Hemostat", "Sterility": "Sterile", "Structure": "Shear-weave"}</t>
+          <t>{"Absorbability": "Fully absorbable", "Absorption Time": "7-14 days", "Form": "Shear-weave", "Intended Use": "control bleeding in tooth extractions and oral surgery", "Product Type": "Absorbable hemostat", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfphj.jpg</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
+      <c r="Y141" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Z141" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:54+00:00</t>
-        </is>
-      </c>
+      <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>9ab73a892933cf6d</t>
+          <t>2026-10-20T04:50:37+00:00</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>18b571a74e8b1b15</t>
         </is>
       </c>
     </row>
@@ -19626,38 +20331,43 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>{"Absorbability": "absorbable", "Absorption Capacity": "up to 40 times its own weight", "Easy to handle": "compressible, does not require any cutting.", "Material": "porcine gelatin", "Solubility": "water insoluble", "Sterility": "sterile"}</t>
+          <t>{"Absorbability": "Absorbable", "Absorption Capacity": "up to 40 times its own weight", "Form": "Sponge", "Intended Use": "hemostatic use by applying to a bleeding surface", "Material": "Porcine gelatin", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
+          <t>{"Easy to handle": "compressible, does not require any cutting."}</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpjk.jpg</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>Safco SureStitch Sutures (PFEMN)</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
+      <c r="Y142" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="Z142" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:46:46+00:00</t>
-        </is>
-      </c>
+      <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>fd89594fac4a70bc</t>
+          <t>2026-10-20T04:50:29+00:00</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>12cb16c21d774a9a</t>
         </is>
       </c>
     </row>
@@ -19757,29 +20467,34 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfhik.jpg</t>
         </is>
       </c>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr">
+      <c r="X143" t="inlineStr"/>
+      <c r="Y143" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y143" t="inlineStr">
+      <c r="Z143" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:47:54+00:00</t>
-        </is>
-      </c>
+      <c r="AA143" t="inlineStr"/>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>8edfa2e49879132d</t>
+          <t>2026-10-20T04:51:23+00:00</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>efd9c00afde6207e</t>
         </is>
       </c>
     </row>
@@ -19889,38 +20604,43 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>{"Color": "matte blue", "Count Per Box": "300 gloves per box", "Cuff Style": "beaded", "Material": "nitrile", "Powder Status": "powder-free", "Texture": "textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 2.9 mils", "Type": "exam gloves"}</t>
+          <t>{"Color": "Matte blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured", "Thickness": "at palm 2.5 mils; at fingertip 2.9 mils"}</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drccc_2.jpg</t>
         </is>
       </c>
-      <c r="W144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
+      <c r="Y144" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y144" t="inlineStr">
+      <c r="Z144" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:01+00:00</t>
-        </is>
-      </c>
+      <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>8e5fae0802a283a1</t>
+          <t>2026-10-20T04:52:18+00:00</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>7dfb6ab5bfc93623</t>
         </is>
       </c>
     </row>
@@ -20022,38 +20742,43 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>{"Color": "Ocean blue", "Cuff Style": "Beaded cuff", "Latex Content": "Latex-free", "Material": "Chloroprene", "Powder Status": "Powder-free", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Ocean blue", "Cuff Style": "Beaded", "Latex Content": "Latex-free", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drdaq.jpg</t>
         </is>
       </c>
-      <c r="W145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ)</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
+      <c r="Y145" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y145" t="inlineStr">
+      <c r="Z145" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:48:29+00:00</t>
-        </is>
-      </c>
+      <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>6a78e269374b27d6</t>
+          <t>2026-10-20T04:51:53+00:00</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>ea88a4aa2297eda7</t>
         </is>
       </c>
     </row>
@@ -20148,34 +20873,39 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>{"Brand": "SW Safety", "Color": "Royal Blue", "Feature": "Reinforced palm", "Grade": "Medical grade", "Model Number": "TF-95RB", "Product Name": "TrueForm Exam Glove", "Texture": "Textured fingertips", "Thickness": "3.1 MIL"}</t>
+          <t>{"Color": "Royal Blue", "Texture": "Textured fingertips and reinforced palm", "Thickness": "3.1 MIL"}</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcdc.jpg</t>
         </is>
       </c>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr">
+      <c r="X146" t="inlineStr"/>
+      <c r="Y146" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y146" t="inlineStr">
+      <c r="Z146" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:13+00:00</t>
-        </is>
-      </c>
+      <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>1271239337708613</t>
+          <t>2026-10-20T04:52:28+00:00</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>addf9642695b78fc</t>
         </is>
       </c>
     </row>
@@ -20283,38 +21013,43 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Box": "100 gloves per box", "Cuff Style": "Beaded cuff", "Finish": "Textured whole hand finish", "Latex Protein Content": "50μg or less"}</t>
+          <t>{"Color": "Natural color", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less of latex protein", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drbaz.jpg</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>Safco Durasoft Latex (DRBBK); Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X147" t="inlineStr">
+      <c r="Y147" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y147" t="inlineStr">
+      <c r="Z147" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:44+00:00</t>
-        </is>
-      </c>
+      <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>e9a38700236a9ec2</t>
+          <t>2026-10-20T04:52:53+00:00</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>71afbedea1dd2df3</t>
         </is>
       </c>
     </row>
@@ -20414,33 +21149,38 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drvcd_lc.jpg</t>
         </is>
       </c>
-      <c r="W148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Surpass Gloves (DRCCS); Safco Nitrilex Prevail Gloves (DRCCJ); Safco EZ Green Chloroprene Gloves (DRDAP); Safco Nitrilex (DRCAL)</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
+      <c r="Y148" t="inlineStr">
         <is>
           <t>deterministic</t>
         </is>
       </c>
-      <c r="Y148" t="inlineStr">
+      <c r="Z148" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:35+00:00</t>
-        </is>
-      </c>
+      <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>25c217f6654e91d2</t>
+          <t>2026-10-20T04:52:45+00:00</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>e4cefe61236c7576</t>
         </is>
       </c>
     </row>
@@ -20549,38 +21289,43 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Box": "100 gloves", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.4 mils; at fingertip 3.2 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.4 mils; at fingertip 3.2 mils"}</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drcaj_2.jpg</t>
         </is>
       </c>
-      <c r="W149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>Safco Nitrilex (DRCAL); Safco Nitrilex UltraSoft Gloves (DRCBN); Safco Nitrilex Prevail Gloves (DRCCJ); Safco Nitrilex Surpass Gloves (DRCCS); Safco EZ Green Chloroprene Gloves (DRDAP)</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
+      <c r="Y149" t="inlineStr">
         <is>
           <t>deterministic+llm</t>
         </is>
       </c>
-      <c r="Y149" t="inlineStr">
+      <c r="Z149" t="inlineStr">
         <is>
           <t>valid</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>2026-10-20T01:49:00+00:00</t>
-        </is>
-      </c>
+      <c r="AA149" t="inlineStr"/>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>3795a45d20dfa20a</t>
+          <t>2026-10-20T04:52:17+00:00</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>e4af04e793dc39f5</t>
         </is>
       </c>
     </row>

--- a/output/products.xlsx
+++ b/output/products.xlsx
@@ -655,14 +655,14 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>{"Absorbability": "Non-resorbable", "Form": "Gauze", "Intended Use": "For external use", "Packaging": "Individual sterile pouches", "Sterility": "Sterile"}</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpaj.jpg</t>
@@ -675,7 +675,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -686,12 +686,12 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:12+00:00</t>
+          <t>2026-10-20T05:27:36+00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>a74ea92372a2f049</t>
+          <t>f8c6e402c60c0a08</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>{"Color": "Medical blue", "Count Per Pack": "200", "Material": "Nitrile", "Product Type": "Dental exam gloves"}</t>
+          <t>{"Color": "Medical blue", "Count Per Pack": "200", "Material": "Nitrile", "Product Type": "Dental exam gloves", "Standards": "fentanyl-tested and chemo-approved"}</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -819,12 +819,12 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:46+00:00</t>
+          <t>2026-10-20T05:28:10+00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>6063202603aec413</t>
+          <t>1ca58497f6468863</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:42+00:00</t>
+          <t>2026-10-20T05:28:06+00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 1.2"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Processing Method": "Non-chlorinated"}</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1105,12 +1105,12 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:29+00:00</t>
+          <t>2026-10-20T05:27:53+00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>eb5bb3290a6f8229</t>
+          <t>404c00cae28f9a8e</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:40+00:00</t>
+          <t>2026-10-20T05:28:04+00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>{"Coating": "Soothing aloe", "Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Latex exam gloves", "Texture": "Fully textured"}</t>
+          <t>{"Coating": "Aloe", "Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Texture": "Textured"}</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1385,12 +1385,12 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:40+00:00</t>
+          <t>2026-10-20T05:29:04+00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3667091f1ec453f0</t>
+          <t>6064f80eb3572939</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>{"Color": "Aqua", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured whole hand", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
+          <t>{"Coating": "Lanolin and Vitamin E", "Color": "Aqua", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured whole hand", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Surface Treatment": "Chlorinated"}</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1531,12 +1531,12 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:08+00:00</t>
+          <t>2026-10-20T05:28:32+00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>6ed02127ecf9eca1</t>
+          <t>e2f64e5468d2085c</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>{"Color": "Aqua blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip3.5 mils; ±0.8"}</t>
+          <t>{"Color": "Aqua blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip3.5 mils; ±0.8"}</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1676,12 +1676,12 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:43+00:00</t>
+          <t>2026-10-20T05:28:07+00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>59c59052ba26799f</t>
+          <t>86f4e9e85464e4ce</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>{"Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8mils; at fingertips 3.1 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Blue", "Count Per Pack": "300 gloves", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8mils; at fingertips 3.1 mils"}</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1822,12 +1822,12 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:27+00:00</t>
+          <t>2026-10-20T05:27:51+00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>92bc5d268c71541c</t>
+          <t>2d2389853b1f2134</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured full finger", "Thickness": "at palm 3.2 mils; at fingertip 4.0 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured full finger finish", "Thickness": "at palm 3.2 mils; at fingertip 4.0 mils"}</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1968,12 +1968,12 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:44+00:00</t>
+          <t>2026-10-20T05:28:08+00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>064bf3ce420f78b6</t>
+          <t>494bf040d812ab03</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>{"Color": "Purple", "Count Per Pack": "300 gloves per box (270 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 3.0 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Purple", "Count Per Pack": "300 gloves per box (270 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 3.0 mils"}</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2114,12 +2114,12 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:26+00:00</t>
+          <t>2026-10-20T05:27:50+00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>c0c6cba04170af52</t>
+          <t>15278ddda063c180</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>{"Color": "Pink", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertips 2.7 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Pink", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertips 2.7 mils"}</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2261,12 +2261,12 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:35+00:00</t>
+          <t>2026-10-20T05:27:59+00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>316a01c91862aecd</t>
+          <t>862fb373e2432896</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Fully-textured", "Thickness": "at palm 5.0 mils; at fingertips 6.0 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Fully-textured", "Thickness": "at palm 5.0 mils; at fingertips 6.0 mils"}</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2401,12 +2401,12 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:55+00:00</t>
+          <t>2026-10-20T05:28:19+00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>82a9a384ae6d862d</t>
+          <t>491332f392bfd689</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10", "Texture": "Honeycomb textured fingertips and palms"}</t>
+          <t>{"Coating": "Polymer coated for easy donning", "Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Texture": "Honeycomb textured fingertips and palms"}</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2546,12 +2546,12 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:52+00:00</t>
+          <t>2026-10-20T05:28:16+00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>3a026fdb2064c889</t>
+          <t>f13f2e0348e8e67a</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "100 gloves", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Texture": "Honeycomb textured fingertips and palms"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Texture": "Honeycomb"}</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2691,12 +2691,12 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:45+00:00</t>
+          <t>2026-10-20T05:28:09+00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>9c88238bbcf48b06</t>
+          <t>3d9c7faff4951e5d</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>{"Color": "Indigo blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Indigo blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2837,12 +2837,12 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:49+00:00</t>
+          <t>2026-10-20T05:28:13+00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>7239b5c593b319d3</t>
+          <t>0c4dcb680bc6e0a7</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Latex exam gloves", "Texture": "Micro-textured"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Latex exam gloves", "Texture": "Micro-textured"}</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2982,12 +2982,12 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:33+00:00</t>
+          <t>2026-10-20T05:27:57+00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>7375eb993f5dbaaf</t>
+          <t>c6ca1d4173003efa</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>{"Color": "Teal green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Coating": "Polymer coated for easy donning", "Color": "Teal green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3127,12 +3127,12 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:47+00:00</t>
+          <t>2026-10-20T05:28:11+00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>c6a3b4605a1ab2a2</t>
+          <t>37227455fdd31c8d</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 4.0 mils; at fingertip 5.2 mils; ± 1.2"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10", "Texture": "Textured fingertip finish", "Thickness": "at palm 4.0 mils; at fingertip 5.2 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3271,12 +3271,12 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:54+00:00</t>
+          <t>2026-10-20T05:28:18+00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>c1cad9bf24563bdd</t>
+          <t>5c29f0ee35a0ae28</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>{"Color": "Indigo blue", "Count Per Pack": "300 gloves per box (270 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Indigo blue", "Count Per Pack": "300 gloves per box (270 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile powder-free exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.2 mils; at fingertips 3.2 mils"}</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3417,12 +3417,12 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:38+00:00</t>
+          <t>2026-10-20T05:28:02+00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>cb335e2f746c24bc</t>
+          <t>bdcbbf69ee0d6c56</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.0 mils; at fingertip 3.8 mils"}</t>
+          <t>{"Coating": "Polymer coated for easy donning", "Color": "Blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.0 mils; at fingertip 3.8 mils"}</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3562,12 +3562,12 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:39+00:00</t>
+          <t>2026-10-20T05:28:03+00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>c70e00eaae5db7d1</t>
+          <t>a7beec607aef8bb2</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Color": "Translucent pink", "Form": "Syringe delivery system", "Product Type": "Visible light cured periodontal dressing", "Texture": "Firm, elastic"}</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Taste": "Tasteless"}</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3684,7 +3684,7 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3695,12 +3695,12 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:06+00:00</t>
+          <t>2026-10-20T05:27:30+00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4e8a46dbb3549d2b</t>
+          <t>1161fc26e70cd3ee</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>{"Color": "Aqua", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
+          <t>{"Coating": "Lanolin and Vitamin E", "Color": "Aqua", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand", "Thickness": "at palm 3.2 mils; at fingertips 4.0 mils"}</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3841,12 +3841,12 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:13+00:00</t>
+          <t>2026-10-20T05:28:37+00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3460beb4eee3f3ef</t>
+          <t>c025890a56ac86e5</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Texture": "Micro-textured whole hand finish"}</t>
+          <t>{"Coating": "Polymer", "Color": "Natural", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Packs Per Case": "10", "Texture": "Micro-textured"}</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3986,12 +3986,12 @@
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:29+00:00</t>
+          <t>2026-10-20T05:28:53+00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ad9830e581f443a0</t>
+          <t>1f4d74d1e0caa006</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Chloroprene examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils; ±0.2"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Green", "Count Per Pack": "200", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Chloroprene", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils; ±0.2"}</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -4131,12 +4131,12 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:57+00:00</t>
+          <t>2026-10-20T05:28:21+00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>86b93e7a7fca3016</t>
+          <t>0dc26ca27943f077</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3 mils"}</t>
+          <t>{"Color": "White", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 3 mils"}</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -4275,12 +4275,12 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:35+00:00</t>
+          <t>2026-10-20T05:28:59+00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>d2bf19f47334d16f</t>
+          <t>b91900c919c833e3</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>{"Color": "Cobalt blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 2.0 mils"}</t>
+          <t>{"Color": "Cobalt blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertips 2.0 mils"}</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Chlorination": "Non-chlorinated"}</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4421,12 +4421,12 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:28+00:00</t>
+          <t>2026-10-20T05:27:52+00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>e169b5970445974f</t>
+          <t>1b1c69842c94b100</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip", "Thickness": "at palm 3 mils; at fingertip 4 mils; ± 0.8"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Texture": "Textured fingertip", "Thickness": "at palm 3 mils; at fingertip 4 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -4565,12 +4565,12 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:36+00:00</t>
+          <t>2026-10-20T05:28:00+00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>fd11434fc73e9e9c</t>
+          <t>c69ecacc0c160dc7</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4710,12 +4710,12 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:25+00:00</t>
+          <t>2026-10-20T05:27:49+00:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>df077f2a95c990e1</t>
+          <t>5d5ae13ee5c234c2</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "300 gloves per box (250 size XL)", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness At Fingertip": "2.2 mils", "Thickness At Palm": "2.0 mils"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness At Fingertip": "2.2 mils", "Thickness At Palm": "2.0 mils"}</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4849,12 +4849,12 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:15+00:00</t>
+          <t>2026-10-20T05:28:39+00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>f53dc050b968c019</t>
+          <t>a92053a99610dd40</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Black", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4988,12 +4988,12 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:31+00:00</t>
+          <t>2026-10-20T05:27:55+00:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ea74cad2190899cf</t>
+          <t>fee663e68f4b3920</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Coating": "Polymer coating for easy donning", "Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "No protein claim", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -5133,12 +5133,12 @@
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:46+00:00</t>
+          <t>2026-10-20T05:29:10+00:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>71a8bda9f47fcc42</t>
+          <t>5f15f67780548480</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>{"Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0mils; at fingertips 2.7mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0mils; at fingertips 2.7mils"}</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -5278,12 +5278,12 @@
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:41+00:00</t>
+          <t>2026-10-20T05:28:05+00:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>4c9d9ff22a856471</t>
+          <t>77c3962a6a761be8</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "200", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10", "Texture": "Textured", "Thickness": "at palm 3.2 mils; at fingertip 3.4 mils"}</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5421,12 +5421,12 @@
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:09+00:00</t>
+          <t>2026-10-20T05:28:33+00:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>58895b2b64d0e26d</t>
+          <t>39902a64bea9aca6</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Product Type": "Surgical dressing and periodontal pack", "Texture": "Cohesive"}</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -5543,7 +5543,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -5554,12 +5554,12 @@
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:04+00:00</t>
+          <t>2026-10-20T05:27:28+00:00</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>e0408648d9c279de</t>
+          <t>607077726a48f1e3</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Material": "Non-eugenol", "Product Type": "Surgical dressing and periodontal pack", "Texture": "Extremely pliable and cohesive"}</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -5670,7 +5670,7 @@
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5681,12 +5681,12 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:17+00:00</t>
+          <t>2026-10-20T05:27:41+00:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>e97a1fafe4ea3551</t>
+          <t>36cf8fed10a156df</t>
         </is>
       </c>
     </row>
@@ -5791,12 +5791,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Standards": "FDA Approved"}</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Activation Method": "Squeeze, Shake, Apply", "Country of Origin": "USA"}</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5822,12 +5822,12 @@
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:57+00:00</t>
+          <t>2026-10-20T05:27:21+00:00</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>3f84814a54864fee</t>
+          <t>52e5ac7b49cb85ae</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Fully absorbable", "Absorption Time": "16 weeks", "Intended Use": "osteogenesis during extraction socket preservation, ridge augmentation, periodontal defect repair or other grafting procedures", "Material": "Purified porcine Type-I peritoneum membrane", "Product Type": "Membrane"}</t>
+          <t>{"Absorption Time": "16 weeks", "Form": "Membrane", "Intended Use": "osteogenesis during extraction socket preservation, ridge augmentation, periodontal defect repair or other grafting procedures", "Material": "Purified porcine Type-I peritoneum"}</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -5968,12 +5968,12 @@
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:34+00:00</t>
+          <t>2026-10-20T05:26:58+00:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2903664669b50f40</t>
+          <t>66b0bdad29ec98e0</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "100", "Intended Use": "Dental and clinical examination procedures", "Material": "Powder-free nitrile", "Packaging": "100 gloves per bag", "Powder Status": "Powder-free", "Product Type": "Nitrile Exam Gloves", "Sizes Available": "XS, S, M, L, XL", "Sterility": "Non-sterile", "Texture": "Fingertip textured", "Thickness": "Approximately 2.2–2.5 mil"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100 gloves per bag", "Intended Use": "Dental and clinical examination procedures", "Material": "Powder-free nitrile", "Packaging": "100 gloves per bag", "Powder Status": "Powder-free", "Product Type": "Nitrile Exam Gloves", "Sizes Available": "XS, S, M, L, XL", "Sterility": "Non-sterile", "Texture": "Fingertip textured", "Thickness": "Approximately 2.2–2.5 mil"}</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -6136,12 +6136,12 @@
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:50+00:00</t>
+          <t>2026-10-20T05:28:14+00:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>134f283d7122b758</t>
+          <t>2d5314dfcd84461d</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100", "Cuff Style": "Beaded", "Packs Per Case": "10", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -6280,12 +6280,12 @@
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:20+00:00</t>
+          <t>2026-10-20T05:28:44+00:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>3da7b3acca9238a9</t>
+          <t>a889f04e319f9680</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5 mils; ± 0.8"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.3 mils; at fingertip 5 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:27+00:00</t>
+          <t>2026-10-20T05:28:51+00:00</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3fafc4475cb125c2</t>
+          <t>edd40e21bb610239</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>{"Coating": "Lanolin and Vitamin E", "Color": "Blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam glove", "Texture": "Textured fingertip", "Thickness": "at palm 3.5 mils; at fingertip 3.8 mils"}</t>
+          <t>{"Coating": "Vitamin E and lanolin", "Color": "Blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam glove", "Thickness": "at palm 3.5 mils; at fingertip 3.8 mils"}</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -6570,12 +6570,12 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:16+00:00</t>
+          <t>2026-10-20T05:28:40+00:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>b7656234338a5733</t>
+          <t>d2d179ec1e77fb20</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100 gloves per box (50 left/right pairs)", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.5 mils; at fingertip 4 mils; ± 0.8"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "White", "Count Per Pack": "100 gloves per box (50 left/right pairs)", "Cuff Style": "Beaded", "Fit": "Left/Right hand specific", "Texture": "Textured whole hand finish", "Thickness": "at palm 3.5 mils; at fingertip 4 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -6714,12 +6714,12 @@
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:21+00:00</t>
+          <t>2026-10-20T05:28:45+00:00</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>687c0f6935decc2a</t>
+          <t>f70c69ce537be990</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>{"Color": "Wintergreen", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured"}</t>
+          <t>{"Coating": "Lanolin and Vitamin E", "Color": "Wintergreen", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand"}</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -6855,12 +6855,12 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:14+00:00</t>
+          <t>2026-10-20T05:28:38+00:00</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>a6f64f55ff28a1f7</t>
+          <t>8ee2b4a50fa04613</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>{"Form": "Ground", "Product Type": "Dental powder", "Standards": "ISO 11137-2 Method 1", "Sterility": "Sterile"}</t>
+          <t>{"Product Type": "Ground dental powder", "Standards": "ISO 11137-2 Method 1", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Sterility Assurance Level": "10(-6)"}</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6986,12 +6986,12 @@
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:49+00:00</t>
+          <t>2026-10-20T05:27:13+00:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1c9156efc3139ae0</t>
+          <t>33c5d50da24c35a7</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>{"Color": "Natural latex color", "Cuff Style": "Beaded", "Length": "11.6\" (295mm)", "Material": "Latex", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured finish", "Thickness": "at palm 7.5 mils; at fingertips: 8.0 mils"}</t>
+          <t>{"Color": "Natural latex", "Count Per Pack": "50 pairs (100 gloves)", "Cuff Style": "Beaded", "Fit": "Right/left hand specific", "Length": "11.6\" (295mm)", "Material": "Latex", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured", "Thickness": "at palm 7.5 mils; at fingertips: 8.0 mils"}</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -7131,12 +7131,12 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:31+00:00</t>
+          <t>2026-10-20T05:28:55+00:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>9931a24a25af8190</t>
+          <t>fcbc83da110b86a1</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Material": "Plastic handle with stainless steel blade", "Product Type": "Disposable scalpel", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -7253,7 +7253,7 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -7264,12 +7264,12 @@
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:08+00:00</t>
+          <t>2026-10-20T05:27:32+00:00</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>60c47c60c2316ea7</t>
+          <t>ba2c8a064e712e7e</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:13+00:00</t>
+          <t>2026-10-20T05:27:37+00:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Material": "Plastic handle", "Product Type": "Disposable scalpel", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -7528,7 +7528,7 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
@@ -7539,12 +7539,12 @@
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:10+00:00</t>
+          <t>2026-10-20T05:27:34+00:00</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>8578b87d43dd84f6</t>
+          <t>1b234ec8ad6d2ca6</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>{"Color": "Natural latex", "Count Per Pack": "50 pairs (100 gloves) per box", "Cuff Style": "Beaded", "Material": "Latex", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Natural latex color", "Count Per Pack": "50 pairs (100 gloves)", "Cuff Style": "Beaded", "Fit": "Right/left hand specific", "Material": "Latex", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured finish"}</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -7677,12 +7677,12 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:37+00:00</t>
+          <t>2026-10-20T05:29:01+00:00</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>dcb7f705b0ac83b1</t>
+          <t>143196f3bb9040b9</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>{"Color": "Off White", "Count Per Pack": "100 gloves per box", "Fit": "Ambidextrous", "Length": "9.5\"", "Material": "Latex", "Packs Per Case": "100 gloves per box, 10 boxes per case", "Powder Status": "Powder-free", "Sizes Available": "TPFS small , TPFM medium , TPFL large", "Texture": "Textured fingertips", "Thickness": "5.5 mil"}</t>
+          <t>{"Color": "Off White", "Count Per Pack": "100 gloves per box", "Fit": "Ambidextrous", "Length": "9.5\"", "Material": "Latex", "Packs Per Case": "100 gloves per box, 10 boxes per case", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Sizes Available": "TPFS small , TPFM medium , TPFL large", "Texture": "Textured fingertips", "Thickness": "5.5 mil"}</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -7817,12 +7817,12 @@
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:25+00:00</t>
+          <t>2026-10-20T05:28:49+00:00</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>4f70a243193a8eca</t>
+          <t>598902763a86f1e8</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>{"Form": "Seamless swaging", "Texture": "Super-smooth", "Thickness": "micro-thin"}</t>
+          <t>{"Material": "Stainless steel", "Texture": "Micro-thin, super-smooth finish"}</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -7954,12 +7954,12 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:45+00:00</t>
+          <t>2026-10-20T05:27:09+00:00</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>61b268586ee7441c</t>
+          <t>ba52a96d45e85588</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>{"Color": "Royal blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.0 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Royal blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.0 mils"}</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -8101,12 +8101,12 @@
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:07+00:00</t>
+          <t>2026-10-20T05:28:31+00:00</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>6ac724ce47fd0ce2</t>
+          <t>6ca673a4dc6ab34d</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -8209,14 +8209,14 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
+          <t>{"Material": "Stainless steel", "Sterility": "gamma-sterilized"}</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflvv.jpg</t>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
@@ -8240,12 +8240,12 @@
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:38+00:00</t>
+          <t>2026-10-20T05:27:02+00:00</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>358aad82addc83d2</t>
+          <t>cb02d750f817e236</t>
         </is>
       </c>
     </row>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Fingertip textured", "Thickness": "at palm 3.0 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Chloroprene (Neoprene)", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Fingertip textured", "Thickness": "at palm 3.0 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -8386,12 +8386,12 @@
       <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:34+00:00</t>
+          <t>2026-10-20T05:28:58+00:00</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>5897124ef17ec0e1</t>
+          <t>f9adde99fe2ba8de</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>{"Material": "Collagen-based", "Product Type": "Bone augmentation material", "Sterility": "Sterile"}</t>
+          <t>{"Material": "Collagen-based", "Product Type": "Collagen-based bone augmentation material", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -8526,12 +8526,12 @@
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:33+00:00</t>
+          <t>2026-10-20T05:26:57+00:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>6d7a26e9b43829ca</t>
+          <t>910db7d0feb03a80</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>{"Color": "Cobalt", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 1.9 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Cobalt", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 1.9 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -8669,12 +8669,12 @@
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:34+00:00</t>
+          <t>2026-10-20T05:27:58+00:00</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>a31002078a3096ac</t>
+          <t>eb2e60be398e3eb7</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Absorbability": "Fully resorbable", "Form": "Particulate", "Material": "Synthetic", "Product Type": "Bone grafting material"}</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -8791,7 +8791,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
@@ -8802,12 +8802,12 @@
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:56+00:00</t>
+          <t>2026-10-20T05:27:20+00:00</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>5de7e9330e91ea00</t>
+          <t>14099985b1cc389e</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.5 mils; at fingertip 4.7 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.5 mils; at fingertip 4.7 mils"}</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -8941,12 +8941,12 @@
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:54+00:00</t>
+          <t>2026-10-20T05:29:18+00:00</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5123adfb139d8ea8</t>
+          <t>5f1548dabc40f683</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:51+00:00</t>
+          <t>2026-10-20T05:28:15+00:00</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Fully absorbable", "Color": "White", "Material": "Collagen", "Packaging": "Individually packaged", "Product Type": "Collagen wound dressing", "Sterility": "Sterile", "Texture": "Porous, pliable"}</t>
+          <t>{"Absorbability": "Absorbable", "Color": "White", "Material": "Type I bovine collagen", "Packaging": "Individually packaged", "Product Type": "Collagen wound dressing", "Sterility": "Sterile", "Texture": "Porous, pliable"}</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -9222,12 +9222,12 @@
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:46+00:00</t>
+          <t>2026-10-20T05:27:10+00:00</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>f5b6a58bac5ab522</t>
+          <t>9b64b456f0f0f71f</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Absorbable", "Count Per Pack": "1", "Intended Use": "guided tissue regeneration procedures in periodontal defects to enhance regeneration of the periodontal apparatus", "Material": "Purified bovine tendon", "Sterility": "Sterile", "Texture": "Pliable; does not become slippery when hydrated"}</t>
+          <t>{"Absorbability": "Absorbable", "Count Per Pack": "1 per box", "Intended Use": "guided tissue regeneration procedures in periodontal defects", "Material": "Purified bovine tendon", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -9355,12 +9355,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:21+00:00</t>
+          <t>2026-10-20T05:27:45+00:00</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>d9dae4d74c7bfdf1</t>
+          <t>660c33916ea471ee</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>{"Absorption Time": "10 to 14 days", "Material": "Bovine tendon", "Product Type": "Hemostatic absorbable collagen material"}</t>
+          <t>{"Absorbability": "Absorbable", "Absorption Time": "10 to 14 days", "Form": "Cylindrical", "Intended Use": "application to moist or bleeding oral wounds created during dental surgery to control bleeding and protect the surface of the wound from further injury", "Material": "Collagen"}</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -9492,12 +9492,12 @@
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:43+00:00</t>
+          <t>2026-10-20T05:27:07+00:00</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>e4b735a68ce342ef</t>
+          <t>796b1477bb10e08d</t>
         </is>
       </c>
     </row>
@@ -9592,14 +9592,14 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
+          <t>{"Absorption Time": "10 to 14 days", "Material": "Collagen", "Packaging": "Individually packaged", "Sterility": "Sterile", "Texture": "Thin, soft, pliable"}</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W65" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfpfp.jpg</t>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
@@ -9623,12 +9623,12 @@
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:05+00:00</t>
+          <t>2026-10-20T05:27:29+00:00</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>a540c286613db54b</t>
+          <t>a148f5b7dc020d90</t>
         </is>
       </c>
     </row>
@@ -9730,14 +9730,14 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>{"Form": "Fabric", "Product Type": "Topical hemostatic dressing", "Sterility": "Sterile"}</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W66" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/m/e/medicom-hemostat-20-box.jpg</t>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
@@ -9761,12 +9761,12 @@
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:36+00:00</t>
+          <t>2026-10-20T05:27:00+00:00</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>7316e2997c19a832</t>
+          <t>eb65d7657794cab8</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>{"Coating": "Flock-lined", "Color": "Lilac", "Count Per Pack": "3 pairs per box", "Cuff Style": "Flat", "Product Type": "Utility gloves", "Texture": "Textured whole hand finish", "Thickness": "0.38mm"}</t>
+          <t>{"Color": "Lilac", "Count Per Pack": "3 pairs", "Cuff Style": "Flat", "Fit": "Left/right-hand fitted", "Material": "Nitrile", "Thickness": "0.38mm"}</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -9906,12 +9906,12 @@
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:43+00:00</t>
+          <t>2026-10-20T05:29:07+00:00</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>aff6cc2a8dddfe6f</t>
+          <t>48ee1114767a5f12</t>
         </is>
       </c>
     </row>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>{"Color": "Aegean blue", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
+          <t>{"Color": "Aegean blue", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -10052,12 +10052,12 @@
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:11+00:00</t>
+          <t>2026-10-20T05:28:35+00:00</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>78b4fe61ad5fe2f3</t>
+          <t>44ffb96831d5ac64</t>
         </is>
       </c>
     </row>
@@ -10158,12 +10158,12 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Form": "Flexible", "Material": "Plastic outer wrap", "Product Type": "Single use cold pack"}</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Activation Method": "Squeeze to activate", "Therapy Duration": "20 minutes"}</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -10174,7 +10174,7 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -10185,12 +10185,12 @@
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:01+00:00</t>
+          <t>2026-10-20T05:27:25+00:00</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>b104b6e61b0f9900</t>
+          <t>93121758a370924d</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>{"Material": "Collagen", "Packaging": "Individually packaged", "Product Type": "Collagen wound dressing", "Sterility": "Sterile"}</t>
+          <t>{"Absorption Time": "10 to 14 days", "Material": "Collagen", "Product Type": "Collagen Wound Dressing", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -10316,12 +10316,12 @@
       <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:18+00:00</t>
+          <t>2026-10-20T05:27:42+00:00</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>0b51d35e026620dc</t>
+          <t>53d3e4497be23597</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:07+00:00</t>
+          <t>2026-10-20T05:27:31+00:00</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>{"Sterility": "Sterile"}</t>
+          <t>{"Latex Content": "not manufactured with latex", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -10582,12 +10582,12 @@
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:11+00:00</t>
+          <t>2026-10-20T05:27:35+00:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>f771dca6ab2ff31e</t>
+          <t>d218101bef71f029</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>{"Color": "Lavender", "Count Per Pack": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertips", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
+          <t>{"Color": "Lavender", "Count Per Pack": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertips", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -10728,12 +10728,12 @@
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:24+00:00</t>
+          <t>2026-10-20T05:27:48+00:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>35b8eac5eb378e2f</t>
+          <t>9ff1fcc10c4d3cb1</t>
         </is>
       </c>
     </row>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>{"Standards": "ISO 9001"}</t>
+          <t>{"Standards": "FDA, QSR, and U.S.P. specifications"}</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Needle Type": "reverse cutting"}</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10865,12 +10865,12 @@
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:48+00:00</t>
+          <t>2026-10-20T05:27:12+00:00</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>aa8656caa4eaf516</t>
+          <t>80fff4966ba3951a</t>
         </is>
       </c>
     </row>
@@ -10979,12 +10979,12 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>{"Color": "Azure blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.5 mils; at fingertip 2.6 mils"}</t>
+          <t>{"Color": "Azure blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 2.6 mils"}</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Chlorination Status": "Non-chlorinated"}</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -11010,12 +11010,12 @@
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:22+00:00</t>
+          <t>2026-10-20T05:28:46+00:00</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>d217021b3be69a5d</t>
+          <t>fda61246c08d8243</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box (X-large 180 gloves per box)", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box (X-large 180 gloves per box)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Intended Use": "Tested for use with chemotherapy drugs", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.9 mils"}</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -11150,12 +11150,12 @@
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:55+00:00</t>
+          <t>2026-10-20T05:29:19+00:00</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>54a61278da15d813</t>
+          <t>785977ac3c800862</t>
         </is>
       </c>
     </row>
@@ -11257,12 +11257,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "200 gloves", "Cuff Style": "Beaded", "Packs Per Case": "10 boxes", "Texture": "Textured fingertips", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Texture": "Textured fingertips", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Surface Treatment": "Chlorinated"}</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -11288,12 +11288,12 @@
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:52+00:00</t>
+          <t>2026-10-20T05:29:16+00:00</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>8381cf6c54dd50f0</t>
+          <t>25be8222430f4d57</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Neoprene (polychloroprene)", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertips", "Thickness": "at palm 5.1 mils; at fingertip 6.3 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Neoprene (polychloroprene)", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertips", "Thickness": "at palm 5.1 mils; at fingertip 6.3 mils"}</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -11434,12 +11434,12 @@
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:38+00:00</t>
+          <t>2026-10-20T05:29:02+00:00</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>888b079d18a5deb1</t>
+          <t>eff41311684f08b5</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -11578,12 +11578,12 @@
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:47+00:00</t>
+          <t>2026-10-20T05:29:11+00:00</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>074db92f980a3b47</t>
+          <t>43f13ab8de50fe8d</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Coating": "Polymer coating for easy donning", "Color": "Natural color", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less of latex protein", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -11723,12 +11723,12 @@
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:19+00:00</t>
+          <t>2026-10-20T05:28:43+00:00</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>81927d85be87ca5a</t>
+          <t>3a1797742ffa75e8</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.7 mils; at fingertip 6.3 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Black", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured whole hand finish", "Thickness": "at palm 4.7 mils; at fingertip 6.3 mils"}</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -11868,12 +11868,12 @@
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:44+00:00</t>
+          <t>2026-10-20T05:29:08+00:00</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>0bdf713dfaa239d3</t>
+          <t>801d4a007b5b7d5b</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
+          <t>{"Color": "Black", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 4.3 mils"}</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -12013,12 +12013,12 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:24+00:00</t>
+          <t>2026-10-20T05:28:48+00:00</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>c0e302964a92d9ad</t>
+          <t>bbaab31854c4e8f2</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100", "Cuff Style": "Beaded", "Packs Per Case": "10", "Texture": "Textured fingertip", "Thickness": "at palm 2.6 mils; at fingertip 3.7 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.6 mils; at fingertip 3.7 mils"}</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -12157,12 +12157,12 @@
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:50+00:00</t>
+          <t>2026-10-20T05:29:14+00:00</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>08e3fdfee505accb</t>
+          <t>7ca6a92f71a27dfe</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded", "Packs Per Case": "10", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "250 gloves per box (230 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -12301,12 +12301,12 @@
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:32+00:00</t>
+          <t>2026-10-20T05:27:56+00:00</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>fa36acf4d8879709</t>
+          <t>2e2fed9bf18dcc2e</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.9 mils; at fingertip 5.1 mils"}</t>
+          <t>{"Coating": "Polymer coated for easy donning", "Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Chloroprene", "Powder Status": "Powder-free", "Product Type": "Chloroprene exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.9 mils; at fingertip 5.1 mils"}</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -12448,12 +12448,12 @@
       <c r="AA85" t="inlineStr"/>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:37+00:00</t>
+          <t>2026-10-20T05:28:01+00:00</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>dda8b74944fd09a8</t>
+          <t>03e10ed5ce28d126</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured whole hand", "Thickness": "at palm 5.1 mils; at fingertip 6.7 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured whole hand finish", "Thickness": "at palm 5.1 mils; at fingertip 6.7 mils"}</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -12594,12 +12594,12 @@
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:42+00:00</t>
+          <t>2026-10-20T05:29:06+00:00</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>6451d7e7fd9c0d77</t>
+          <t>898b1fb9f9c3aff7</t>
         </is>
       </c>
     </row>
@@ -12704,7 +12704,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Powder Status": "Powder-free", "Product Type": "Chloroprene examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Green", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Chloroprene (neoprene)", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.8 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -12735,12 +12735,12 @@
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:48+00:00</t>
+          <t>2026-10-20T05:29:12+00:00</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>4705dd88561ff5db</t>
+          <t>f97b8e3ee62604f8</t>
         </is>
       </c>
     </row>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>{"Color": "Cobalt blue", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Cobalt blue", "Count Per Pack": "300 gloves per box (250 for x-large)", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -12879,12 +12879,12 @@
       <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:30+00:00</t>
+          <t>2026-10-20T05:27:54+00:00</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>747f798fb02212fc</t>
+          <t>ea9b61c6c14f21f8</t>
         </is>
       </c>
     </row>
@@ -12982,14 +12982,14 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
+          <t>{"Material": "Swiss carbon steel", "Packaging": "Two VCI strips", "Product Type": "Surgical blades"}</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W89" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflqt.jpg</t>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
@@ -13013,12 +13013,12 @@
       <c r="AA89" t="inlineStr"/>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:19+00:00</t>
+          <t>2026-10-20T05:27:43+00:00</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>651d099ad9d07744</t>
+          <t>196f62ca6353907e</t>
         </is>
       </c>
     </row>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>{"Product Type": "Surgical Blades", "Sizes Available": "10-25", "Standards": "ISO-7740, ISO-13485"}</t>
+          <t>{"Material": "Swiss carbon steel", "Sizes Available": "10-25", "Standards": "ISO-7740, ISO-13485"}</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -13145,12 +13145,12 @@
       <c r="AA90" t="inlineStr"/>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:58+00:00</t>
+          <t>2026-10-20T05:27:22+00:00</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>f8ca7225924e1d85</t>
+          <t>440767e9c5323e38</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>{"Coating": "RediPass needle coating", "Material": "300 Series stainless steel", "Packaging": "Low-memory racetrack tray", "Product Type": "Surgical-grade sutures", "Sterility": "Sterile"}</t>
+          <t>{"Coating": "RediPass needle coating", "Packaging": "Racetrack tray", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -13284,12 +13284,12 @@
       <c r="AA91" t="inlineStr"/>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:00+00:00</t>
+          <t>2026-10-20T05:27:24+00:00</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>524acf02a642768f</t>
+          <t>e39ddf7c8f9129c9</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Standards": "ISO 13485"}</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -13405,7 +13405,7 @@
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
@@ -13416,12 +13416,12 @@
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:09+00:00</t>
+          <t>2026-10-20T05:27:33+00:00</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>6eede0e878c531e6</t>
+          <t>5b2629dd8f8601a1</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 0.8"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.1 mils; at fingertip 3.9 mils; ± 0.8"}</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -13561,12 +13561,12 @@
       <c r="AA93" t="inlineStr"/>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:51+00:00</t>
+          <t>2026-10-20T05:29:15+00:00</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>7ffe8018cf438b24</t>
+          <t>2b64c18b3656f9b6</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "50 pairs (100 gloves) per box", "Cuff Style": "Beaded", "Length": "12\"", "Material": "Nitrile", "Packs Per Case": "4 boxes", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured", "Thickness At Fingertip": "7.0 mils"}</t>
+          <t>{"Color": "White", "Count Per Pack": "50 pairs (100 gloves) per box", "Cuff Style": "Beaded", "Fit": "Right/left hand specific", "Length": "12\"", "Material": "Nitrile", "Packs Per Case": "4 boxes in a case", "Powder Status": "Powder-free", "Product Type": "Surgical gloves", "Sterility": "Sterile", "Texture": "Textured finish", "Thickness At Fingertip": "7.0 mils"}</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -13706,12 +13706,12 @@
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:33+00:00</t>
+          <t>2026-10-20T05:28:57+00:00</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>aae305130c1789a1</t>
+          <t>e1f8224256d321bc</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>{"Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Vinyl", "Packs Per Case": "10 boxes in a case", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Soft, form fitting", "Thickness": "at palm 3.2 mils; at fingertip 2.3 mils"}</t>
+          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Vinyl", "Packs Per Case": "10 boxes in a case", "Powder Status": "Powder-free", "Product Type": "Vinyl examination gloves", "Texture": "Smooth finish", "Thickness": "at palm 3.2 mils; at fingertip 2.3 mils"}</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Chlorination Status": "Non-chlorinated"}</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -13846,12 +13846,12 @@
       <c r="AA95" t="inlineStr"/>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:23+00:00</t>
+          <t>2026-10-20T05:28:47+00:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>9b994fb1e1a51071</t>
+          <t>c76549602450b8f7</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>{"Color": "Emerald green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.1 mils; at fingertip 4 mils"}</t>
+          <t>{"Color": "Emerald green", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.1 mils; at fingertip 4 mils"}</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -13985,12 +13985,12 @@
       <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:56+00:00</t>
+          <t>2026-10-20T05:28:20+00:00</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>8bb635a37f6549d2</t>
+          <t>bf0c4f5d8a3a36a2</t>
         </is>
       </c>
     </row>
@@ -14092,12 +14092,12 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Intended Use": "treats intraoral wounds and lesions", "Product Type": "Hydrogel dressing", "Standards": "FDA approved"}</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Drug Content": "Contains no drugs", "Safety": "Safe if swallowed", "Weight": "10g"}</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -14108,7 +14108,7 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
@@ -14119,12 +14119,12 @@
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:31+00:00</t>
+          <t>2026-10-20T05:26:55+00:00</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>203a0886af81d89e</t>
+          <t>2fbfbd4d7efa31eb</t>
         </is>
       </c>
     </row>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>{"Absorption Capacity": "35x its weight", "Absorption Time": "3-7 days", "Form": "Cubes", "Packaging": "Individually packaged", "Product Type": "Absorbable gelatin sponge hemostat", "Standards": "USP", "Sterility": "Sterile"}</t>
+          <t>{"Absorption Capacity": "up to 35x its weight", "Absorption Time": "3-7 days", "Form": "Cubes", "Packaging": "Individually packaged", "Product Type": "Absorbable gelatin sponge hemostat", "Standards": "USP", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -14256,12 +14256,12 @@
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:16+00:00</t>
+          <t>2026-10-20T05:27:40+00:00</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>523b234884c4d821</t>
+          <t>3314e66a60fee1f1</t>
         </is>
       </c>
     </row>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Intended Use": "relief from dry sockets and oral pain", "Material": "Essential oils and other natural ingredients"}</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Application Dosage": "8 to 10 drops", "Medication Status": "Non-medicated"}</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -14372,7 +14372,7 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
@@ -14383,12 +14383,12 @@
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:03+00:00</t>
+          <t>2026-10-20T05:27:27+00:00</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>47fce997d059015e</t>
+          <t>a068ec972843c0eb</t>
         </is>
       </c>
     </row>
@@ -14485,12 +14485,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>{"Packaging": "Jars", "Sterility": "Sterile"}</t>
+          <t>{"Form": "Sponge strips", "Intended Use": "Extraction socket grafting, implant placement, osseous ridge repair, sinus augmentations", "Material": "Mineralized cancellous bone allograft", "Packaging": "Jars", "Product Type": "Bone allograft", "Sterility": "Sterile", "Texture": "Pliable and resilient sponge matrix"}</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Characteristics": "Quickly becomes well vascularized following placement", "Properties": "osteoconductive and osteoinductive scaffold"}</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -14516,12 +14516,12 @@
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:30+00:00</t>
+          <t>2026-10-20T05:26:54+00:00</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>411e2ded0fb3131f</t>
+          <t>8e17ce16c2d30436</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -14616,14 +14616,14 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
+          <t>{"Material": "100% laminar cortical bone", "Packaging": "Pre-hydrated and ready to use"}</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W101" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrg.jpg</t>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
@@ -14647,12 +14647,12 @@
       <c r="AA101" t="inlineStr"/>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:40+00:00</t>
+          <t>2026-10-20T05:27:04+00:00</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>85756c5d0ef7f76b</t>
+          <t>4adc23a6dfdef246</t>
         </is>
       </c>
     </row>
@@ -14747,14 +14747,14 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
+          <t>{"Intended Use": "socket grafting, GBR, sinus augmentation, bone grafting procedures", "Material": "Demineralized cortical bone fibers", "Particle Size": "1-1.5mm", "Product Type": "Bone allograft"}</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W102" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfwrf.jpg</t>
@@ -14767,7 +14767,7 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
@@ -14778,12 +14778,12 @@
       <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:41+00:00</t>
+          <t>2026-10-20T05:27:05+00:00</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>f63a59f225d4ff1e</t>
+          <t>6d4c857eaddfd0c4</t>
         </is>
       </c>
     </row>
@@ -14878,12 +14878,12 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>{"Particle Size": "0.5 – 1.0mm"}</t>
+          <t>{"Material": "50/50 blend of cortical and cancellous bone", "Particle Size": "0.5 – 1.0mm"}</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Demineralized Percentage": "30%", "Mineralized Percentage": "70%"}</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -14909,12 +14909,12 @@
       <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:32+00:00</t>
+          <t>2026-10-20T05:26:56+00:00</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>ee3b4e0b24664a68</t>
+          <t>2d76ed089a00af2f</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Color": "Violet", "Form": "High viscosity", "Product Type": "Cyanoacrylate oral tissue adhesive"}</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -15032,7 +15032,7 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
@@ -15043,12 +15043,12 @@
       <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:53+00:00</t>
+          <t>2026-10-20T05:27:17+00:00</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>0bdc0152695b68f0</t>
+          <t>c30cdab78c194bda</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Material": "Series 300 Stainless Steel", "Product Type": "Suture needles", "Texture": "High-polished finish"}</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -15165,7 +15165,7 @@
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
@@ -15176,12 +15176,12 @@
       <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:44+00:00</t>
+          <t>2026-10-20T05:27:08+00:00</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>8f1f61222a7a24ad</t>
+          <t>0f4dff6a113f03dd</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>{"Color": "Natural white", "Count Per Pack": "100", "Cuff Style": "Beaded", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Natural white", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip"}</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -15315,12 +15315,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:56+00:00</t>
+          <t>2026-10-20T05:29:20+00:00</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>0bb8c1b6df5d1424</t>
+          <t>2c1545f78914997c</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>{"AQL": "1.5", "Color": "Black", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Fully textured", "Thickness": "5.0 mil"}</t>
+          <t>{"AQL": "1.5", "Color": "Black", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Fully textured", "Thickness": "5.0 mil"}</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -15463,12 +15463,12 @@
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:32+00:00</t>
+          <t>2026-10-20T05:28:56+00:00</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>75ca628579679d1a</t>
+          <t>250aee164c064a19</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Coating": "Polymer bonded interior", "Color": "White", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -15608,12 +15608,12 @@
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:49+00:00</t>
+          <t>2026-10-20T05:29:13+00:00</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>cfcf1f6033c4b4e1</t>
+          <t>52974ea5e45afd30</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>{"Color": "Dark lavender blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.0mils; at fingertips 3.5 mils"}</t>
+          <t>{"Color": "Dark lavender blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.0mils; at fingertips 3.5 mils"}</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -15753,12 +15753,12 @@
       <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:30+00:00</t>
+          <t>2026-10-20T05:28:54+00:00</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>171fa39f4bb61820</t>
+          <t>7e6c7c7aa99ab04b</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.0 mils."}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes in a case", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.0 mils."}</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -15893,12 +15893,12 @@
       <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:41+00:00</t>
+          <t>2026-10-20T05:29:05+00:00</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>54b6652cac118553</t>
+          <t>70e26dd2b8b1b8bf</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Packs Per Case": "10 boxes", "Texture": "Textured"}</t>
+          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -16037,12 +16037,12 @@
       <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:39+00:00</t>
+          <t>2026-10-20T05:29:03+00:00</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>d19b823764ec6346</t>
+          <t>e1148f21baefcf8c</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>{"Color": "Purple", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 4.7 mils; at fingertip 5.9 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Purple", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 4.7 mils; at fingertip 5.9 mils"}</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -16182,12 +16182,12 @@
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:36+00:00</t>
+          <t>2026-10-20T05:29:00+00:00</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>cf37adf9200ed510</t>
+          <t>c8e2fd09318e01c8</t>
         </is>
       </c>
     </row>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>{"Color": "Vibrant blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Intended Use": "Dental, veterinarian, mortuary, cleaning, tattoo", "Length": "9.5\"", "Material": "Nitrile", "Packs Per Case": "100 gloves per box, 10 boxes per case", "Powder Status": "Powder-free", "Texture": "Micro-textured outer surface", "Thickness": "4.0 MIL"}</t>
+          <t>{"Color": "Vibrant blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Intended Use": "Dental, veterinarian, mortuary, cleaning, tattoo", "Length": "9.5\"", "Material": "Nitrile", "Packs Per Case": "100 gloves per box, 10 boxes per case", "Powder Status": "Powder-free", "Texture": "Micro-textured", "Thickness": "4.0 MIL"}</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -16331,12 +16331,12 @@
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:05+00:00</t>
+          <t>2026-10-20T05:28:29+00:00</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>c371723e102bca40</t>
+          <t>7da279538fbbc1c3</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Absorbable", "Absorption Time": "4-8 weeks", "Form": "Cut to size and shape", "Intended Use": "barrier to protect PDL development from fast growing tissues"}</t>
+          <t>{"Absorbability": "Absorbable", "Absorption Time": "4-8 weeks", "Form": "Cut to size and shape", "Material": "Type I bovine Achilles tendon collagen", "Texture": "Non-slippery when wet"}</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -16462,12 +16462,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:22+00:00</t>
+          <t>2026-10-20T05:27:46+00:00</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>a951ea12082753ce</t>
+          <t>675d7fc598cb3763</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
       <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:54+00:00</t>
+          <t>2026-10-20T05:27:18+00:00</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -16731,7 +16731,7 @@
       <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:35+00:00</t>
+          <t>2026-10-20T05:26:59+00:00</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -16844,12 +16844,12 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>{"Color": "Dark blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Texture": "Textured", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
+          <t>{"Color": "Dark blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Processing": "Non-chlorinated"}</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -16875,12 +16875,12 @@
       <c r="AA117" t="inlineStr"/>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:26+00:00</t>
+          <t>2026-10-20T05:28:50+00:00</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>d90b26a9114e14df</t>
+          <t>2be8e9724cf1381e</t>
         </is>
       </c>
     </row>
@@ -16988,7 +16988,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
+          <t>{"Color": "Blue", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.8 mils"}</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:48+00:00</t>
+          <t>2026-10-20T05:28:12+00:00</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>b4a3eba4eac589c0</t>
+          <t>b3e8746164eaddff</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>{"Color": "White", "Count Per Pack": "100 gloves", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Natural latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Micro-textured"}</t>
+          <t>{"Color": "Natural latex white", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Micro-textured"}</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -17161,12 +17161,12 @@
       <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:59+00:00</t>
+          <t>2026-10-20T05:28:23+00:00</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>d1266b547214d4cb</t>
+          <t>324c1d92b7f0d0b4</t>
         </is>
       </c>
     </row>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>{"Color": "Green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Powder Status": "Powder-free", "Product Type": "Chloroprene examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.0 mils; at fingertips 3.5 mils"}</t>
+          <t>{"Color": "Green", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Chloroprene", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.0 mils; at fingertips 3.5 mils"}</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -17306,12 +17306,12 @@
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:06+00:00</t>
+          <t>2026-10-20T05:28:30+00:00</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>c1baa629eaa1742d</t>
+          <t>9163a205b49f74f2</t>
         </is>
       </c>
     </row>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>{"Color": "Black", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Powder-free nitrile exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Black", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.0 mils; at fingertip 2.3 mils"}</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -17453,12 +17453,12 @@
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:01+00:00</t>
+          <t>2026-10-20T05:28:25+00:00</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>3244e07d4f08f48d</t>
+          <t>1c0af4bc12eb0080</t>
         </is>
       </c>
     </row>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Texture": "Textured fingertip", "Thickness At Fingertip": "3.0 mils", "Thickness At Palm": "2.5 mils"}</t>
+          <t>{"Coating": "Polymer coated", "Color": "Blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Thickness At Fingertip": "3.0 mils", "Thickness At Palm": "2.5 mils"}</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -17600,12 +17600,12 @@
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:03+00:00</t>
+          <t>2026-10-20T05:28:27+00:00</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>ff94ed1850bfc8bc</t>
+          <t>9fc9c73c6175992e</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Micro-textured", "Thickness": "at palm 4.3 mils; at fingertip 5.1 mils; ± 1.2"}</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -17746,12 +17746,12 @@
       <c r="AA123" t="inlineStr"/>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:04+00:00</t>
+          <t>2026-10-20T05:28:28+00:00</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>88924b13592b1f60</t>
+          <t>ba0bda5f6f62e43b</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>{"Color": "Lavender blue", "Count Per Pack": "200", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 3.2 mils; at fingertips 3.5 mils"}</t>
+          <t>{"Coating": "Chlorinated", "Color": "Lavender blue", "Count Per Pack": "200 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 3.2 mils; at fingertips 3.5 mils"}</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -17892,12 +17892,12 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:00+00:00</t>
+          <t>2026-10-20T05:28:24+00:00</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>b0bcfa821478fd28</t>
+          <t>725a21aba59e8feb</t>
         </is>
       </c>
     </row>
@@ -18003,7 +18003,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>{"Coating": "Colloidal oatmeal", "Color": "Robin Egg Blue", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Standards": "Chemotherapy drug tested per ASTM D6978", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.3 mils"}</t>
+          <t>{"Coating": "Colloidal oatmeal", "Color": "Robin Egg Blue", "Cuff Style": "Beaded", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Standards": "ASTM D6978", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 3.3 mils"}</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -18034,12 +18034,12 @@
       <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:02+00:00</t>
+          <t>2026-10-20T05:28:26+00:00</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>2b3ef70260916870</t>
+          <t>9e4d73bc1501f2d0</t>
         </is>
       </c>
     </row>
@@ -18150,7 +18150,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "300 gloves", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Standards": "ASTM D6978", "Thickness": "at palm 3.2 mils; at fingertip 3.5 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Standards": "ASTM D6978", "Thickness": "at palm 3.2 mils; at fingertip 3.5 mils"}</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -18177,12 +18177,12 @@
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:58+00:00</t>
+          <t>2026-10-20T05:28:22+00:00</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>f78b674159b13d91</t>
+          <t>6c145280dc49ed78</t>
         </is>
       </c>
     </row>
@@ -18287,12 +18287,12 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Non-absorbable", "Color": "Black", "Form": "Monofilament", "Product Type": "Suture"}</t>
+          <t>{"Color": "Black", "Form": "Braided"}</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>{"Chromic gut (catgut)": "Produced with the same precision and quality materials as plain gut, plus treated with chromic acid salts to decrease tissue reactivity and provide a slower absorption rate.", "Plain gut (catgut)": "Made of first quality raw material, catgut has extremely high tensile strength. Every strand is precision polished to a uniform diameter, permitting smooth and secure knotting."}</t>
+          <t>{"Chromic gut (catgut)": "Produced with the same precision and quality materials as plain gut, plus treated with chromic acid salts to decrease tissue reactivity and provide a slower absorption rate.", "Needle Type": "Reverse cutting", "Plain gut (catgut)": "Made of first quality raw material, catgut has extremely high tensile strength. Every strand is precision polished to a uniform diameter, permitting smooth and secure knotting."}</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -18314,12 +18314,12 @@
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:42+00:00</t>
+          <t>2026-10-20T05:27:06+00:00</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>0118fb78c0c5cfa9</t>
+          <t>d53193f749c64b6e</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Material": "Stainless steel", "Packaging": "Individually packaged", "Product Type": "Retractable blade scalpel", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -18436,7 +18436,7 @@
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
@@ -18447,12 +18447,12 @@
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:20+00:00</t>
+          <t>2026-10-20T05:27:44+00:00</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>e8a89720a6f2c659</t>
+          <t>d35dc1a18cdf901e</t>
         </is>
       </c>
     </row>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -18556,12 +18556,12 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>{"Form": "European Round", "Intended Use": "cutting gingival tissue and making surgical incisions", "Product Type": "Scalpel handle"}</t>
+          <t>{"Intended Use": "cutting gingival tissue and making surgical incisions"}</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>{"Features": "metric ruler"}</t>
+          <t>{"Angle": "30 degree", "Design Feature": "greater rotational movement with fingertip control", "Feature": "metric ruler", "Handle Style": "#3"}</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -18587,12 +18587,12 @@
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:15+00:00</t>
+          <t>2026-10-20T05:27:39+00:00</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>23379befd492fe78</t>
+          <t>68e11addeb9e4e90</t>
         </is>
       </c>
     </row>
@@ -18695,7 +18695,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50µg or less", "Packs Per Case": "10 boxes", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Coating": "Polymer coated for easy donning", "Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50µg or less", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -18726,12 +18726,12 @@
       <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:10+00:00</t>
+          <t>2026-10-20T05:28:34+00:00</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>043167d279a4019a</t>
+          <t>024fcad5fb9aa4ef</t>
         </is>
       </c>
     </row>
@@ -18842,7 +18842,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>{"Color": "Natural", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand"}</t>
+          <t>{"Coating": "USP grade Lanolin and Vitamin E", "Color": "Natural", "Count Per Pack": "100 gloves", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less", "Material": "Latex", "Packs Per Case": "10 boxes", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -18873,12 +18873,12 @@
       <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:12+00:00</t>
+          <t>2026-10-20T05:28:36+00:00</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>14e6cb47a3ef865e</t>
+          <t>1497f49980231523</t>
         </is>
       </c>
     </row>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>{"Form": "IV bags", "Material": "Not manufactured with latex, PVC or DEHP"}</t>
+          <t>{"Intended Use": "extracellular fluid replacement, treatment of metabolic alkalosis in the presence of fluid loss and mild sodium depletion", "Latex Content": "not manufactured with latex"}</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -19012,12 +19012,12 @@
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:47+00:00</t>
+          <t>2026-10-20T05:27:11+00:00</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>7567137ae403d4b7</t>
+          <t>48dcad7dd9518707</t>
         </is>
       </c>
     </row>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Latex Content": "Latex-free", "Material": "Plastic", "Product Type": "Sodium chloride injection", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
@@ -19135,7 +19135,7 @@
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
@@ -19146,12 +19146,12 @@
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:52+00:00</t>
+          <t>2026-10-20T05:27:16+00:00</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>3a6e75b0aed4f099</t>
+          <t>46a70a541cf9df1c</t>
         </is>
       </c>
     </row>
@@ -19246,14 +19246,14 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
+          <t>{"Material": "Hard oxide", "Product Type": "FG bur"}</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W134" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflwh.jpg</t>
@@ -19266,7 +19266,7 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
@@ -19277,12 +19277,12 @@
       <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:39+00:00</t>
+          <t>2026-10-20T05:27:03+00:00</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>68b440e2fce1d69c</t>
+          <t>2987187c5744e0d3</t>
         </is>
       </c>
     </row>
@@ -19385,12 +19385,12 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>{"Coating": "Contains no bacteriostatic or antimicrobial agents", "Form": "IV bags", "Latex Content": "not manufactured with latex", "Sterility": "Sterile"}</t>
+          <t>{"Coating": "Contains no bacteriostatic or antimicrobial agents", "Form": "Clear, colorless, odorless liquid", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>{"Pyrogen Status": "nonpyrogenic"}</t>
+          <t>{"Container Material": "not manufactured with latex, PVC or DEHP", "Pyrogenicity": "nonpyrogenic", "Tonicity": "hypotonic"}</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
@@ -19412,12 +19412,12 @@
       <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:50+00:00</t>
+          <t>2026-10-20T05:27:14+00:00</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>3f335619253ec134</t>
+          <t>f5b2c1cb1ffdfb7a</t>
         </is>
       </c>
     </row>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>{"Sizes Available": "3, 4"}</t>
+          <t>{"Intended Use": "tissue separation, and other procedures that require a sharp surgical blade to puncture or cut", "Material": "Stainless steel", "Sterility": "Non-sterile"}</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -19554,12 +19554,12 @@
       <c r="AA136" t="inlineStr"/>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:14+00:00</t>
+          <t>2026-10-20T05:27:38+00:00</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>6d14b366eaa1c123</t>
+          <t>e058f12278324bbe</t>
         </is>
       </c>
     </row>
@@ -19660,14 +19660,14 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
+          <t>{"Count Per Pack": "100", "Packaging": "Foil packs", "Sterility": "Sterile"}</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W137" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pfljq.jpg</t>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
@@ -19691,12 +19691,12 @@
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:59+00:00</t>
+          <t>2026-10-20T05:27:23+00:00</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>86b00bde719ef60e</t>
+          <t>5577019f66709bb0</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Packaging": "Individual foil packs"}</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -19813,7 +19813,7 @@
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
@@ -19824,12 +19824,12 @@
       <c r="AA138" t="inlineStr"/>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:02+00:00</t>
+          <t>2026-10-20T05:27:26+00:00</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>caded21b9bec16d3</t>
+          <t>e2d7ac4ed53dfbe4</t>
         </is>
       </c>
     </row>
@@ -19924,14 +19924,14 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
+          <t>{"Form": "Microsurgical and standard", "Intended Use": "cutting gingival tissue and making surgical incisions", "Material": "Carbon steel"}</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W139" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/p/f/pflta.jpg</t>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
@@ -19955,12 +19955,12 @@
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:55+00:00</t>
+          <t>2026-10-20T05:27:19+00:00</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>78707d036fff6cb5</t>
+          <t>8e7996369c33e993</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Count Per Pack": "100", "Packaging": "Individual foil packs", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
@@ -20077,7 +20077,7 @@
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
@@ -20088,12 +20088,12 @@
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:51+00:00</t>
+          <t>2026-10-20T05:27:15+00:00</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>18324d4067f6b55f</t>
+          <t>96eb6efbbbea178c</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Fully absorbable", "Absorption Time": "7-14 days", "Form": "Shear-weave", "Intended Use": "control bleeding in tooth extractions and oral surgery", "Product Type": "Absorbable hemostat", "Sterility": "Sterile"}</t>
+          <t>{"Absorbability": "Fully absorbable", "Absorption Time": "7-14 days", "Form": "Shear-weave", "Intended Use": "control bleeding in tooth extractions and oral surgery", "Material": "Oxidized regenerated cellulose", "Product Type": "Absorbable hemostat", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -20219,12 +20219,12 @@
       <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:37+00:00</t>
+          <t>2026-10-20T05:27:01+00:00</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>18b571a74e8b1b15</t>
+          <t>841a651dc4ad31af</t>
         </is>
       </c>
     </row>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>{"Absorbability": "Absorbable", "Absorption Capacity": "up to 40 times its own weight", "Form": "Sponge", "Intended Use": "hemostatic use by applying to a bleeding surface", "Material": "Porcine gelatin", "Sterility": "Sterile"}</t>
+          <t>{"Absorbability": "Bioresorbable", "Absorption Capacity": "up to 40 times its own weight", "Color": "Off-white", "Material": "Porcine gelatin", "Product Type": "Absorbable sponge", "Sterility": "Sterile"}</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -20362,12 +20362,12 @@
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-20T04:50:29+00:00</t>
+          <t>2026-10-20T05:26:53+00:00</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>12cb16c21d774a9a</t>
+          <t>8a267b06042894a6</t>
         </is>
       </c>
     </row>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>in_stock</t>
+          <t>drop_ship</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Product Type": "Surgeon's Needles"}</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -20478,7 +20478,7 @@
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
@@ -20489,12 +20489,12 @@
       <c r="AA143" t="inlineStr"/>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:23+00:00</t>
+          <t>2026-10-20T05:27:47+00:00</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>efd9c00afde6207e</t>
+          <t>8ce253ed361f6751</t>
         </is>
       </c>
     </row>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>{"Color": "Matte blue", "Count Per Pack": "300", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured", "Thickness": "at palm 2.5 mils; at fingertip 2.9 mils"}</t>
+          <t>{"Color": "Matte blue", "Count Per Pack": "300 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Powder Status": "Powder-free", "Product Type": "Nitrile exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.5 mils; at fingertip 2.9 mils"}</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -20635,12 +20635,12 @@
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:18+00:00</t>
+          <t>2026-10-20T05:28:42+00:00</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>7dfb6ab5bfc93623</t>
+          <t>006b41b59bbac3a2</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>{"Color": "Ocean blue", "Cuff Style": "Beaded", "Latex Content": "Latex-free", "Material": "Chloroprene", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
+          <t>{"Color": "Ocean blue", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Content": "Latex-free", "Material": "Chloroprene", "Powder Status": "Powder-free", "Product Type": "Examination gloves", "Texture": "Textured fingertip finish", "Thickness": "at palm 2.4 mils; at fingertip 3.1 mils"}</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -20773,12 +20773,12 @@
       <c r="AA145" t="inlineStr"/>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-20T04:51:53+00:00</t>
+          <t>2026-10-20T05:28:17+00:00</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>ea88a4aa2297eda7</t>
+          <t>51be6b2080e8667f</t>
         </is>
       </c>
     </row>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>{"Color": "Royal Blue", "Texture": "Textured fingertips and reinforced palm", "Thickness": "3.1 MIL"}</t>
+          <t>{"Color": "Royal Blue", "Intended Use": "dental, medical applications as well as veterinarian and dairy", "Product Type": "Exam Glove", "Texture": "Textured fingertips and reinforced palm", "Thickness": "3.1 MIL"}</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -20900,12 +20900,12 @@
       <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:28+00:00</t>
+          <t>2026-10-20T05:28:52+00:00</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>addf9642695b78fc</t>
+          <t>76fea770146f88b0</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>{"Color": "Natural color", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Latex Protein Level": "50μg or less of latex protein", "Texture": "Textured whole hand finish"}</t>
+          <t>{"Color": "Natural color", "Count Per Pack": "100 gloves per box", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Latex Protein Level": "50μg or less of latex protein", "Texture": "Textured whole hand finish"}</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -21044,12 +21044,12 @@
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:53+00:00</t>
+          <t>2026-10-20T05:29:17+00:00</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>71afbedea1dd2df3</t>
+          <t>a8ddaa23546754eb</t>
         </is>
       </c>
     </row>
@@ -21144,14 +21144,14 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
+          <t>{"Color": "White", "Material": "Steel"}</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
       <c r="W148" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/media/catalog/product/d/r/drvcd_lc.jpg</t>
@@ -21164,7 +21164,7 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>deterministic</t>
+          <t>deterministic+llm</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
@@ -21175,12 +21175,12 @@
       <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:45+00:00</t>
+          <t>2026-10-20T05:29:09+00:00</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>e4cefe61236c7576</t>
+          <t>992978782c280dec</t>
         </is>
       </c>
     </row>
@@ -21289,7 +21289,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.4 mils; at fingertip 3.2 mils"}</t>
+          <t>{"Color": "Blue", "Count Per Pack": "100", "Cuff Style": "Beaded", "Fit": "Ambidextrous", "Material": "Nitrile", "Packs Per Case": "10", "Powder Status": "Powder-free", "Product Type": "Exam gloves", "Texture": "Textured fingertip", "Thickness": "at palm 2.4 mils; at fingertip 3.2 mils"}</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -21320,12 +21320,12 @@
       <c r="AA149" t="inlineStr"/>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-20T04:52:17+00:00</t>
+          <t>2026-10-20T05:28:41+00:00</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>e4af04e793dc39f5</t>
+          <t>3761760776e7d801</t>
         </is>
       </c>
     </row>
@@ -33001,7 +33001,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "48/pack"}</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -33022,6 +33022,14 @@
       <c r="M156" t="inlineStr">
         <is>
           <t>In stock</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>48</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
     </row>
@@ -42739,6 +42747,11 @@
           <t>In stock</t>
         </is>
       </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -42806,6 +42819,11 @@
           <t>In stock</t>
         </is>
       </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -42873,6 +42891,11 @@
           <t>In stock</t>
         </is>
       </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -42940,6 +42963,11 @@
           <t>Direct from manufacturer</t>
         </is>
       </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -43509,7 +43537,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "10/pack"}</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
@@ -43530,6 +43558,14 @@
       <c r="M298" t="inlineStr">
         <is>
           <t>In stock</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>10</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
     </row>
@@ -69734,7 +69770,7 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "10/pack"}</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
@@ -69755,6 +69791,14 @@
       <c r="M650" t="inlineStr">
         <is>
           <t>In stock</t>
+        </is>
+      </c>
+      <c r="N650" t="n">
+        <v>10</v>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
     </row>
@@ -69801,7 +69845,7 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "10/pack"}</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
@@ -69822,6 +69866,14 @@
       <c r="M651" t="inlineStr">
         <is>
           <t>Backorder</t>
+        </is>
+      </c>
+      <c r="N651" t="n">
+        <v>10</v>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>pack</t>
         </is>
       </c>
     </row>
@@ -71403,7 +71455,7 @@
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "1/pack"}</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
@@ -71478,7 +71530,7 @@
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "1/pack"}</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -71853,7 +71905,7 @@
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "1/pack"}</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
@@ -71928,7 +71980,7 @@
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"pack": "1/pack"}</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
